--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -773,42 +773,42 @@
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
+          <t>法拉第</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
           <t>小蜥蜴</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>六子</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>霓虹gtr</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>帕梅</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>ps龙</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>ts900</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>divo</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>法拉第</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
@@ -1197,7 +1197,9 @@
       <c r="AN5" s="4" t="n">
         <v>18.17</v>
       </c>
-      <c r="AO5" s="4" t="n"/>
+      <c r="AO5" s="4" t="n">
+        <v>17.85</v>
+      </c>
       <c r="AP5" s="4" t="n"/>
       <c r="AQ5" s="4" t="n"/>
       <c r="AR5" s="4" t="n"/>
@@ -1291,10 +1293,10 @@
       <c r="AP6" s="4" t="n"/>
       <c r="AQ6" s="4" t="n"/>
       <c r="AR6" s="4" t="n"/>
-      <c r="AS6" s="4" t="n">
+      <c r="AS6" s="4" t="n"/>
+      <c r="AT6" s="4" t="n">
         <v>17.89</v>
       </c>
-      <c r="AT6" s="4" t="n"/>
       <c r="AU6" s="4" t="n"/>
       <c r="AV6" s="4" t="n"/>
       <c r="AW6" s="4" t="n"/>
@@ -2058,7 +2060,7 @@
         <v>30.09</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>28</v>
+        <v>27.65</v>
       </c>
       <c r="Z15" s="4" t="n"/>
       <c r="AA15" s="4" t="n"/>
@@ -2224,7 +2226,9 @@
       <c r="Q17" s="4" t="n">
         <v>29.5</v>
       </c>
-      <c r="R17" s="4" t="n"/>
+      <c r="R17" s="4" t="n">
+        <v>28.6</v>
+      </c>
       <c r="S17" s="4" t="n">
         <v>29.5</v>
       </c>
@@ -2522,10 +2526,10 @@
       <c r="AO20" s="4" t="n"/>
       <c r="AP20" s="4" t="n"/>
       <c r="AQ20" s="4" t="n"/>
-      <c r="AR20" s="4" t="n">
+      <c r="AR20" s="4" t="n"/>
+      <c r="AS20" s="4" t="n">
         <v>23.75</v>
       </c>
-      <c r="AS20" s="4" t="n"/>
       <c r="AT20" s="4" t="n"/>
       <c r="AU20" s="4" t="n"/>
       <c r="AV20" s="4" t="n"/>
@@ -3471,10 +3475,10 @@
       <c r="AR31" s="4" t="n"/>
       <c r="AS31" s="4" t="n"/>
       <c r="AT31" s="4" t="n"/>
-      <c r="AU31" s="4" t="n">
+      <c r="AU31" s="4" t="n"/>
+      <c r="AV31" s="4" t="n">
         <v>18.87</v>
       </c>
-      <c r="AV31" s="4" t="n"/>
       <c r="AW31" s="4" t="n"/>
       <c r="AX31" s="4" t="n"/>
       <c r="AY31" s="4" t="n"/>
@@ -3557,10 +3561,10 @@
       </c>
       <c r="AO32" s="4" t="n"/>
       <c r="AP32" s="4" t="n"/>
-      <c r="AQ32" s="4" t="n">
+      <c r="AQ32" s="4" t="n"/>
+      <c r="AR32" s="4" t="n">
         <v>28.79</v>
       </c>
-      <c r="AR32" s="4" t="n"/>
       <c r="AS32" s="4" t="n"/>
       <c r="AT32" s="4" t="n"/>
       <c r="AU32" s="4" t="n"/>
@@ -3656,10 +3660,10 @@
       <c r="AO33" s="4" t="n"/>
       <c r="AP33" s="4" t="n"/>
       <c r="AQ33" s="4" t="n"/>
-      <c r="AR33" s="4" t="n">
+      <c r="AR33" s="4" t="n"/>
+      <c r="AS33" s="4" t="n">
         <v>21.09</v>
       </c>
-      <c r="AS33" s="4" t="n"/>
       <c r="AT33" s="4" t="n"/>
       <c r="AU33" s="4" t="n"/>
       <c r="AV33" s="4" t="n"/>
@@ -4568,10 +4572,10 @@
       <c r="AM44" s="4" t="n"/>
       <c r="AN44" s="4" t="n"/>
       <c r="AO44" s="4" t="n"/>
-      <c r="AP44" s="4" t="n">
+      <c r="AP44" s="4" t="n"/>
+      <c r="AQ44" s="4" t="n">
         <v>22.65</v>
       </c>
-      <c r="AQ44" s="4" t="n"/>
       <c r="AR44" s="4" t="n"/>
       <c r="AS44" s="4" t="n"/>
       <c r="AT44" s="4" t="n"/>
@@ -4993,10 +4997,10 @@
       <c r="AL49" s="4" t="n"/>
       <c r="AM49" s="4" t="n"/>
       <c r="AN49" s="4" t="n"/>
-      <c r="AO49" s="4" t="n">
+      <c r="AO49" s="4" t="n"/>
+      <c r="AP49" s="4" t="n">
         <v>29.75</v>
       </c>
-      <c r="AP49" s="4" t="n"/>
       <c r="AQ49" s="4" t="n"/>
       <c r="AR49" s="4" t="n"/>
       <c r="AS49" s="4" t="n"/>
@@ -5099,10 +5103,10 @@
       <c r="AL50" s="4" t="n"/>
       <c r="AM50" s="4" t="n"/>
       <c r="AN50" s="4" t="n"/>
-      <c r="AO50" s="4" t="n">
+      <c r="AO50" s="4" t="n"/>
+      <c r="AP50" s="4" t="n">
         <v>26.29</v>
       </c>
-      <c r="AP50" s="4" t="n"/>
       <c r="AQ50" s="4" t="n"/>
       <c r="AR50" s="4" t="n"/>
       <c r="AS50" s="4" t="n"/>
@@ -6028,13 +6032,13 @@
       <c r="AM61" s="4" t="n"/>
       <c r="AN61" s="4" t="n"/>
       <c r="AO61" s="4" t="n"/>
-      <c r="AP61" s="4" t="n">
+      <c r="AP61" s="4" t="n"/>
+      <c r="AQ61" s="4" t="n">
         <v>22.3</v>
       </c>
-      <c r="AQ61" s="4" t="n">
+      <c r="AR61" s="4" t="n">
         <v>21.89</v>
       </c>
-      <c r="AR61" s="4" t="n"/>
       <c r="AS61" s="4" t="n"/>
       <c r="AT61" s="4" t="n"/>
       <c r="AU61" s="4" t="n"/>
@@ -6436,7 +6440,9 @@
       <c r="Q66" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="R66" s="4" t="n"/>
+      <c r="R66" s="4" t="n">
+        <v>33.49</v>
+      </c>
       <c r="S66" s="4" t="n"/>
       <c r="T66" s="4" t="n"/>
       <c r="U66" s="4" t="n"/>
@@ -6545,18 +6551,18 @@
       <c r="AL67" s="4" t="n"/>
       <c r="AM67" s="4" t="n"/>
       <c r="AN67" s="4" t="n"/>
-      <c r="AO67" s="4" t="n"/>
+      <c r="AO67" s="4" t="n">
+        <v>17.9</v>
+      </c>
       <c r="AP67" s="4" t="n"/>
       <c r="AQ67" s="4" t="n"/>
       <c r="AR67" s="4" t="n"/>
       <c r="AS67" s="4" t="n"/>
-      <c r="AT67" s="4" t="n">
+      <c r="AT67" s="4" t="n"/>
+      <c r="AU67" s="4" t="n">
         <v>17.8</v>
       </c>
-      <c r="AU67" s="4" t="n"/>
-      <c r="AV67" s="4" t="n">
-        <v>17.9</v>
-      </c>
+      <c r="AV67" s="4" t="n"/>
       <c r="AW67" s="4" t="n"/>
       <c r="AX67" s="4" t="n"/>
       <c r="AY67" s="4" t="n"/>
@@ -6676,7 +6682,7 @@
         <v>32.4</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>31.3</v>
+        <v>31.19</v>
       </c>
       <c r="H69" s="4" t="n">
         <v>31.7</v>
@@ -6948,7 +6954,9 @@
       <c r="S72" s="4" t="n">
         <v>25.3</v>
       </c>
-      <c r="T72" s="4" t="n"/>
+      <c r="T72" s="4" t="n">
+        <v>31.6</v>
+      </c>
       <c r="U72" s="4" t="n"/>
       <c r="V72" s="4" t="n">
         <v>26.1</v>
@@ -8413,27 +8421,27 @@
       </c>
       <c r="BQ1" s="1" t="inlineStr">
         <is>
+          <t>法拉第★6</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
           <t>六子★6</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>霓虹gtr★6</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>ps龙★6</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>ts900★6</t>
-        </is>
-      </c>
-      <c r="BU1" s="1" t="inlineStr">
-        <is>
-          <t>法拉第★6</t>
         </is>
       </c>
       <c r="BV1" s="1" t="inlineStr">
@@ -8880,7 +8888,9 @@
       <c r="AI5" s="4" t="n"/>
       <c r="AJ5" s="4" t="n"/>
       <c r="AK5" s="4" t="n"/>
-      <c r="AL5" s="4" t="n"/>
+      <c r="AL5" s="4" t="n">
+        <v>17.72</v>
+      </c>
       <c r="AM5" s="4" t="n"/>
       <c r="AN5" s="4" t="n"/>
       <c r="AO5" s="4" t="n"/>
@@ -8975,7 +8985,9 @@
       <c r="Z6" s="4" t="n"/>
       <c r="AA6" s="4" t="n"/>
       <c r="AB6" s="4" t="n"/>
-      <c r="AC6" s="4" t="n"/>
+      <c r="AC6" s="4" t="n">
+        <v>17.8</v>
+      </c>
       <c r="AD6" s="4" t="n">
         <v>18.05</v>
       </c>
@@ -9023,10 +9035,10 @@
       <c r="BP6" s="4" t="n"/>
       <c r="BQ6" s="4" t="n"/>
       <c r="BR6" s="4" t="n"/>
-      <c r="BS6" s="4" t="n">
+      <c r="BS6" s="4" t="n"/>
+      <c r="BT6" s="4" t="n">
         <v>17.8</v>
       </c>
-      <c r="BT6" s="4" t="n"/>
       <c r="BU6" s="4" t="n"/>
       <c r="BV6" s="4" t="n"/>
       <c r="BW6" s="4" t="n"/>
@@ -11848,10 +11860,10 @@
       </c>
       <c r="BP32" s="4" t="n"/>
       <c r="BQ32" s="4" t="n"/>
-      <c r="BR32" s="4" t="n">
+      <c r="BR32" s="4" t="n"/>
+      <c r="BS32" s="4" t="n">
         <v>29.2</v>
       </c>
-      <c r="BS32" s="4" t="n"/>
       <c r="BT32" s="4" t="n"/>
       <c r="BU32" s="4" t="n"/>
       <c r="BV32" s="4" t="n"/>
@@ -15627,13 +15639,13 @@
       <c r="BN67" s="4" t="n"/>
       <c r="BO67" s="4" t="n"/>
       <c r="BP67" s="4" t="n"/>
-      <c r="BQ67" s="4" t="n"/>
+      <c r="BQ67" s="4" t="n">
+        <v>18.3</v>
+      </c>
       <c r="BR67" s="4" t="n"/>
       <c r="BS67" s="4" t="n"/>
       <c r="BT67" s="4" t="n"/>
-      <c r="BU67" s="4" t="n">
-        <v>18.3</v>
-      </c>
+      <c r="BU67" s="4" t="n"/>
       <c r="BV67" s="4" t="n"/>
       <c r="BW67" s="4" t="n"/>
       <c r="BX67" s="4" t="n"/>
@@ -16857,7 +16869,9 @@
       <c r="T79" s="4" t="n"/>
       <c r="U79" s="4" t="n"/>
       <c r="V79" s="4" t="n"/>
-      <c r="W79" s="4" t="n"/>
+      <c r="W79" s="4" t="n">
+        <v>22.79</v>
+      </c>
       <c r="X79" s="4" t="n"/>
       <c r="Y79" s="4" t="n"/>
       <c r="Z79" s="4" t="n"/>
@@ -17929,27 +17943,27 @@
       </c>
       <c r="BQ1" s="1" t="inlineStr">
         <is>
+          <t>法拉第★6</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
           <t>六子★6</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>霓虹gtr★6</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>ps龙★6</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>ts900★6</t>
-        </is>
-      </c>
-      <c r="BU1" s="1" t="inlineStr">
-        <is>
-          <t>法拉第★6</t>
         </is>
       </c>
       <c r="BV1" s="1" t="inlineStr">
@@ -18735,12 +18749,12 @@
       <c r="BP6" s="4" t="n"/>
       <c r="BQ6" s="4" t="n"/>
       <c r="BR6" s="4" t="n"/>
-      <c r="BS6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BT6" s="4" t="n"/>
+      <c r="BS6" s="4" t="n"/>
+      <c r="BT6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BU6" s="4" t="n"/>
       <c r="BV6" s="4" t="n"/>
       <c r="BW6" s="4" t="n"/>
@@ -19239,19 +19253,19 @@
       <c r="BN9" s="4" t="n"/>
       <c r="BO9" s="4" t="n"/>
       <c r="BP9" s="4" t="n"/>
-      <c r="BQ9" s="4" t="n"/>
+      <c r="BQ9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BR9" s="4" t="n"/>
-      <c r="BS9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BT9" s="4" t="n"/>
-      <c r="BU9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BS9" s="4" t="n"/>
+      <c r="BT9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BU9" s="4" t="n"/>
       <c r="BV9" s="4" t="n"/>
       <c r="BW9" s="4" t="n"/>
       <c r="BX9" s="4" t="n"/>
@@ -19418,14 +19432,14 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="BR10" s="4" t="n"/>
+      <c r="BR10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BS10" s="4" t="n"/>
       <c r="BT10" s="4" t="n"/>
-      <c r="BU10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BU10" s="4" t="n"/>
       <c r="BV10" s="4" t="n"/>
       <c r="BW10" s="4" t="n"/>
       <c r="BX10" s="4" t="n"/>
@@ -19737,12 +19751,12 @@
       <c r="BN12" s="4" t="n"/>
       <c r="BO12" s="4" t="n"/>
       <c r="BP12" s="4" t="n"/>
-      <c r="BQ12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BR12" s="4" t="n"/>
+      <c r="BQ12" s="4" t="n"/>
+      <c r="BR12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BS12" s="4" t="n"/>
       <c r="BT12" s="4" t="n"/>
       <c r="BU12" s="4" t="n"/>
@@ -20714,14 +20728,14 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="BR18" s="4" t="n"/>
+      <c r="BR18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BS18" s="4" t="n"/>
       <c r="BT18" s="4" t="n"/>
-      <c r="BU18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BU18" s="4" t="n"/>
       <c r="BV18" s="4" t="n"/>
       <c r="BW18" s="4" t="n"/>
       <c r="BX18" s="4" t="n"/>
@@ -21641,15 +21655,15 @@
       <c r="BN24" s="4" t="n"/>
       <c r="BO24" s="4" t="n"/>
       <c r="BP24" s="4" t="n"/>
-      <c r="BQ24" s="4" t="n"/>
+      <c r="BQ24" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BR24" s="4" t="n"/>
       <c r="BS24" s="4" t="n"/>
       <c r="BT24" s="4" t="n"/>
-      <c r="BU24" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BU24" s="4" t="n"/>
       <c r="BV24" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -22703,12 +22717,12 @@
       <c r="BN31" s="4" t="n"/>
       <c r="BO31" s="4" t="n"/>
       <c r="BP31" s="4" t="n"/>
-      <c r="BQ31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BR31" s="4" t="n"/>
+      <c r="BQ31" s="4" t="n"/>
+      <c r="BR31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BS31" s="4" t="n"/>
       <c r="BT31" s="4" t="n"/>
       <c r="BU31" s="4" t="n"/>
@@ -22894,12 +22908,12 @@
       </c>
       <c r="BP32" s="4" t="n"/>
       <c r="BQ32" s="4" t="n"/>
-      <c r="BR32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BS32" s="4" t="n"/>
+      <c r="BR32" s="4" t="n"/>
+      <c r="BS32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BT32" s="4" t="n"/>
       <c r="BU32" s="4" t="n"/>
       <c r="BV32" s="4" t="n"/>
@@ -23809,15 +23823,15 @@
       <c r="BN38" s="4" t="n"/>
       <c r="BO38" s="4" t="n"/>
       <c r="BP38" s="4" t="n"/>
-      <c r="BQ38" s="4" t="n"/>
+      <c r="BQ38" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BR38" s="4" t="n"/>
       <c r="BS38" s="4" t="n"/>
       <c r="BT38" s="4" t="n"/>
-      <c r="BU38" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BU38" s="4" t="n"/>
       <c r="BV38" s="4" t="n"/>
       <c r="BW38" s="4" t="n"/>
       <c r="BX38" s="4" t="n"/>
@@ -24773,12 +24787,12 @@
       <c r="BN44" s="4" t="n"/>
       <c r="BO44" s="4" t="n"/>
       <c r="BP44" s="4" t="n"/>
-      <c r="BQ44" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BR44" s="4" t="n"/>
+      <c r="BQ44" s="4" t="n"/>
+      <c r="BR44" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BS44" s="4" t="n"/>
       <c r="BT44" s="4" t="n"/>
       <c r="BU44" s="4" t="n"/>
@@ -28388,13 +28402,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="BR67" s="4" t="n"/>
+      <c r="BR67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BS67" s="4" t="n"/>
-      <c r="BT67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BT67" s="4" t="n"/>
       <c r="BU67" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -35232,12 +35246,12 @@
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
+          <t>biome</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
           <t>帕梅</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>biome</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
@@ -36458,10 +36472,10 @@
       <c r="AJ20" s="4" t="n"/>
       <c r="AK20" s="4" t="n"/>
       <c r="AL20" s="4" t="n"/>
-      <c r="AM20" s="4" t="n">
+      <c r="AM20" s="4" t="n"/>
+      <c r="AN20" s="4" t="n">
         <v>23.75</v>
       </c>
-      <c r="AN20" s="4" t="n"/>
       <c r="AO20" s="4" t="n"/>
       <c r="AP20" s="4" t="n"/>
       <c r="AQ20" s="4" t="n"/>
@@ -37266,10 +37280,10 @@
       <c r="AJ33" s="4" t="n"/>
       <c r="AK33" s="4" t="n"/>
       <c r="AL33" s="4" t="n"/>
-      <c r="AM33" s="4" t="n">
+      <c r="AM33" s="4" t="n"/>
+      <c r="AN33" s="4" t="n">
         <v>21.09</v>
       </c>
-      <c r="AN33" s="4" t="n"/>
       <c r="AO33" s="4" t="n"/>
       <c r="AP33" s="4" t="n"/>
       <c r="AQ33" s="4" t="n"/>
@@ -38980,10 +38994,10 @@
       <c r="AL61" s="4" t="n">
         <v>22.3</v>
       </c>
-      <c r="AM61" s="4" t="n"/>
-      <c r="AN61" s="4" t="n">
+      <c r="AM61" s="4" t="n">
         <v>21.92</v>
       </c>
+      <c r="AN61" s="4" t="n"/>
       <c r="AO61" s="4" t="n"/>
       <c r="AP61" s="4" t="n"/>
       <c r="AQ61" s="4" t="n"/>
@@ -39648,7 +39662,9 @@
       <c r="AJ72" s="4" t="n"/>
       <c r="AK72" s="4" t="n"/>
       <c r="AL72" s="4" t="n"/>
-      <c r="AM72" s="4" t="n"/>
+      <c r="AM72" s="4" t="n">
+        <v>26.15</v>
+      </c>
       <c r="AN72" s="4" t="n"/>
       <c r="AO72" s="4" t="n"/>
       <c r="AP72" s="4" t="n"/>
@@ -40313,7 +40329,9 @@
         <v>26.59</v>
       </c>
       <c r="G84" s="4" t="n"/>
-      <c r="H84" s="4" t="n"/>
+      <c r="H84" s="4" t="n">
+        <v>27.39</v>
+      </c>
       <c r="I84" s="4" t="n"/>
       <c r="J84" s="4" t="n"/>
       <c r="K84" s="4" t="n"/>
@@ -46832,7 +46850,9 @@
       <c r="N84" s="4" t="n"/>
       <c r="O84" s="4" t="n"/>
       <c r="P84" s="4" t="n"/>
-      <c r="Q84" s="4" t="n"/>
+      <c r="Q84" s="4" t="n">
+        <v>27.6</v>
+      </c>
       <c r="R84" s="4" t="n"/>
       <c r="S84" s="4" t="n"/>
       <c r="T84" s="4" t="n"/>
@@ -56027,7 +56047,11 @@
       <c r="N84" s="4" t="n"/>
       <c r="O84" s="4" t="n"/>
       <c r="P84" s="4" t="n"/>
-      <c r="Q84" s="4" t="n"/>
+      <c r="Q84" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="R84" s="4" t="n"/>
       <c r="S84" s="4" t="n"/>
       <c r="T84" s="4" t="n"/>

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -688,17 +688,17 @@
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
+          <t>速尾</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
           <t>狼崽</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>300+</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>速尾</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
@@ -994,10 +994,10 @@
       <c r="U3" s="4" t="n"/>
       <c r="V3" s="4" t="n"/>
       <c r="W3" s="4" t="n"/>
-      <c r="X3" s="4" t="n">
+      <c r="X3" s="4" t="n"/>
+      <c r="Y3" s="4" t="n">
         <v>29.6</v>
       </c>
-      <c r="Y3" s="4" t="n"/>
       <c r="Z3" s="4" t="n"/>
       <c r="AA3" s="4" t="n"/>
       <c r="AB3" s="4" t="n"/>
@@ -1080,13 +1080,13 @@
       <c r="U4" s="4" t="n"/>
       <c r="V4" s="4" t="n"/>
       <c r="W4" s="4" t="n"/>
-      <c r="X4" s="4" t="n">
+      <c r="X4" s="4" t="n"/>
+      <c r="Y4" s="4" t="n">
         <v>32.29</v>
       </c>
-      <c r="Y4" s="4" t="n">
+      <c r="Z4" s="4" t="n">
         <v>29.65</v>
       </c>
-      <c r="Z4" s="4" t="n"/>
       <c r="AA4" s="4" t="n"/>
       <c r="AB4" s="4" t="n"/>
       <c r="AC4" s="4" t="n"/>
@@ -1168,11 +1168,11 @@
       <c r="U5" s="4" t="n"/>
       <c r="V5" s="4" t="n"/>
       <c r="W5" s="4" t="n"/>
-      <c r="X5" s="4" t="n"/>
+      <c r="X5" s="4" t="n">
+        <v>17.78</v>
+      </c>
       <c r="Y5" s="4" t="n"/>
-      <c r="Z5" s="4" t="n">
-        <v>17.78</v>
-      </c>
+      <c r="Z5" s="4" t="n"/>
       <c r="AA5" s="4" t="n">
         <v>17.5</v>
       </c>
@@ -1435,13 +1435,13 @@
       <c r="V8" s="4" t="n"/>
       <c r="W8" s="4" t="n"/>
       <c r="X8" s="4" t="n">
+        <v>27.94</v>
+      </c>
+      <c r="Y8" s="4" t="n">
         <v>28.9</v>
       </c>
-      <c r="Y8" s="4" t="n">
+      <c r="Z8" s="4" t="n">
         <v>26.998</v>
-      </c>
-      <c r="Z8" s="4" t="n">
-        <v>27.94</v>
       </c>
       <c r="AA8" s="4" t="n"/>
       <c r="AB8" s="4" t="n">
@@ -1780,11 +1780,11 @@
       <c r="U12" s="4" t="n"/>
       <c r="V12" s="4" t="n"/>
       <c r="W12" s="4" t="n"/>
-      <c r="X12" s="4" t="n"/>
+      <c r="X12" s="4" t="n">
+        <v>21.54</v>
+      </c>
       <c r="Y12" s="4" t="n"/>
-      <c r="Z12" s="4" t="n">
-        <v>21.54</v>
-      </c>
+      <c r="Z12" s="4" t="n"/>
       <c r="AA12" s="4" t="n">
         <v>21.3</v>
       </c>
@@ -1869,10 +1869,10 @@
       <c r="V13" s="4" t="n"/>
       <c r="W13" s="4" t="n"/>
       <c r="X13" s="4" t="n"/>
-      <c r="Y13" s="4" t="n">
+      <c r="Y13" s="4" t="n"/>
+      <c r="Z13" s="4" t="n">
         <v>40.25</v>
       </c>
-      <c r="Z13" s="4" t="n"/>
       <c r="AA13" s="4" t="n"/>
       <c r="AB13" s="4" t="n">
         <v>40.3</v>
@@ -2056,13 +2056,13 @@
       <c r="U15" s="4" t="n"/>
       <c r="V15" s="4" t="n"/>
       <c r="W15" s="4" t="n"/>
-      <c r="X15" s="4" t="n">
+      <c r="X15" s="4" t="n"/>
+      <c r="Y15" s="4" t="n">
         <v>30.09</v>
       </c>
-      <c r="Y15" s="4" t="n">
+      <c r="Z15" s="4" t="n">
         <v>27.65</v>
       </c>
-      <c r="Z15" s="4" t="n"/>
       <c r="AA15" s="4" t="n"/>
       <c r="AB15" s="4" t="n">
         <v>28</v>
@@ -2316,10 +2316,10 @@
       <c r="U18" s="4" t="n"/>
       <c r="V18" s="4" t="n"/>
       <c r="W18" s="4" t="n"/>
-      <c r="X18" s="4" t="n">
+      <c r="X18" s="4" t="n"/>
+      <c r="Y18" s="4" t="n">
         <v>24.19</v>
       </c>
-      <c r="Y18" s="4" t="n"/>
       <c r="Z18" s="4" t="n"/>
       <c r="AA18" s="4" t="n">
         <v>23.1</v>
@@ -2593,10 +2593,10 @@
         <v>29.95</v>
       </c>
       <c r="X21" s="4" t="n"/>
-      <c r="Y21" s="4" t="n">
+      <c r="Y21" s="4" t="n"/>
+      <c r="Z21" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="Z21" s="4" t="n"/>
       <c r="AA21" s="4" t="n"/>
       <c r="AB21" s="4" t="n"/>
       <c r="AC21" s="4" t="n"/>
@@ -3180,10 +3180,10 @@
       <c r="U28" s="4" t="n"/>
       <c r="V28" s="4" t="n"/>
       <c r="W28" s="4" t="n"/>
-      <c r="X28" s="4" t="n">
+      <c r="X28" s="4" t="n"/>
+      <c r="Y28" s="4" t="n">
         <v>33.79</v>
       </c>
-      <c r="Y28" s="4" t="n"/>
       <c r="Z28" s="4" t="n"/>
       <c r="AA28" s="4" t="n"/>
       <c r="AB28" s="4" t="n"/>
@@ -3260,10 +3260,10 @@
       <c r="W29" s="4" t="n">
         <v>17.5</v>
       </c>
-      <c r="X29" s="4" t="n">
+      <c r="X29" s="4" t="n"/>
+      <c r="Y29" s="4" t="n">
         <v>19.39</v>
       </c>
-      <c r="Y29" s="4" t="n"/>
       <c r="Z29" s="4" t="n"/>
       <c r="AA29" s="4" t="n"/>
       <c r="AB29" s="4" t="n"/>
@@ -3719,10 +3719,10 @@
       <c r="V34" s="4" t="n"/>
       <c r="W34" s="4" t="n"/>
       <c r="X34" s="4" t="n"/>
-      <c r="Y34" s="4" t="n">
+      <c r="Y34" s="4" t="n"/>
+      <c r="Z34" s="4" t="n">
         <v>33.1</v>
       </c>
-      <c r="Z34" s="4" t="n"/>
       <c r="AA34" s="4" t="n"/>
       <c r="AB34" s="4" t="n"/>
       <c r="AC34" s="4" t="n"/>
@@ -3804,11 +3804,11 @@
         <v>23.69</v>
       </c>
       <c r="W35" s="4" t="n"/>
-      <c r="X35" s="4" t="n"/>
+      <c r="X35" s="4" t="n">
+        <v>22.95</v>
+      </c>
       <c r="Y35" s="4" t="n"/>
-      <c r="Z35" s="4" t="n">
-        <v>22.95</v>
-      </c>
+      <c r="Z35" s="4" t="n"/>
       <c r="AA35" s="4" t="n"/>
       <c r="AB35" s="4" t="n"/>
       <c r="AC35" s="4" t="n"/>
@@ -4380,10 +4380,10 @@
       </c>
       <c r="V42" s="4" t="n"/>
       <c r="W42" s="4" t="n"/>
-      <c r="X42" s="4" t="n">
+      <c r="X42" s="4" t="n"/>
+      <c r="Y42" s="4" t="n">
         <v>22.89</v>
       </c>
-      <c r="Y42" s="4" t="n"/>
       <c r="Z42" s="4" t="n"/>
       <c r="AA42" s="4" t="n"/>
       <c r="AB42" s="4" t="n"/>
@@ -4888,10 +4888,10 @@
       </c>
       <c r="V48" s="4" t="n"/>
       <c r="W48" s="4" t="n"/>
-      <c r="X48" s="4" t="n">
+      <c r="X48" s="4" t="n"/>
+      <c r="Y48" s="4" t="n">
         <v>25.59</v>
       </c>
-      <c r="Y48" s="4" t="n"/>
       <c r="Z48" s="4" t="n"/>
       <c r="AA48" s="4" t="n"/>
       <c r="AB48" s="4" t="n"/>
@@ -4979,10 +4979,10 @@
       </c>
       <c r="W49" s="4" t="n"/>
       <c r="X49" s="4" t="n"/>
-      <c r="Y49" s="4" t="n">
+      <c r="Y49" s="4" t="n"/>
+      <c r="Z49" s="4" t="n">
         <v>29.99</v>
       </c>
-      <c r="Z49" s="4" t="n"/>
       <c r="AA49" s="4" t="n"/>
       <c r="AB49" s="4" t="n"/>
       <c r="AC49" s="4" t="n"/>
@@ -5077,10 +5077,10 @@
       </c>
       <c r="W50" s="4" t="n"/>
       <c r="X50" s="4" t="n"/>
-      <c r="Y50" s="4" t="n">
+      <c r="Y50" s="4" t="n"/>
+      <c r="Z50" s="4" t="n">
         <v>26.79</v>
       </c>
-      <c r="Z50" s="4" t="n"/>
       <c r="AA50" s="4" t="n"/>
       <c r="AB50" s="4" t="n">
         <v>26.6</v>
@@ -5343,10 +5343,10 @@
         <v>31.72</v>
       </c>
       <c r="X53" s="4" t="n"/>
-      <c r="Y53" s="4" t="n">
+      <c r="Y53" s="4" t="n"/>
+      <c r="Z53" s="4" t="n">
         <v>32.09</v>
       </c>
-      <c r="Z53" s="4" t="n"/>
       <c r="AA53" s="4" t="n"/>
       <c r="AB53" s="4" t="n"/>
       <c r="AC53" s="4" t="n"/>
@@ -5470,13 +5470,13 @@
         <v>32.45</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>30.91</v>
+        <v>30.8</v>
       </c>
       <c r="F55" s="4" t="n">
         <v>30.89</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>30.9</v>
+        <v>30.7</v>
       </c>
       <c r="H55" s="4" t="n">
         <v>32</v>
@@ -5679,10 +5679,10 @@
         <v>34.3</v>
       </c>
       <c r="X57" s="4" t="n"/>
-      <c r="Y57" s="4" t="n">
+      <c r="Y57" s="4" t="n"/>
+      <c r="Z57" s="4" t="n">
         <v>34.79</v>
       </c>
-      <c r="Z57" s="4" t="n"/>
       <c r="AA57" s="4" t="n"/>
       <c r="AB57" s="4" t="n"/>
       <c r="AC57" s="4" t="n"/>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="F58" s="4" t="n"/>
       <c r="G58" s="4" t="n">
-        <v>23.4</v>
+        <v>23.42</v>
       </c>
       <c r="H58" s="4" t="n">
         <v>23.8</v>
@@ -5754,10 +5754,10 @@
       <c r="W58" s="4" t="n">
         <v>24.19</v>
       </c>
-      <c r="X58" s="4" t="n">
+      <c r="X58" s="4" t="n"/>
+      <c r="Y58" s="4" t="n">
         <v>26.2</v>
       </c>
-      <c r="Y58" s="4" t="n"/>
       <c r="Z58" s="4" t="n"/>
       <c r="AA58" s="4" t="n"/>
       <c r="AB58" s="4" t="n"/>
@@ -5918,7 +5918,9 @@
       <c r="U60" s="4" t="n"/>
       <c r="V60" s="4" t="n"/>
       <c r="W60" s="4" t="n"/>
-      <c r="X60" s="4" t="n"/>
+      <c r="X60" s="4" t="n">
+        <v>36.5</v>
+      </c>
       <c r="Y60" s="4" t="n"/>
       <c r="Z60" s="4" t="n"/>
       <c r="AA60" s="4" t="n"/>
@@ -6196,11 +6198,11 @@
       <c r="U63" s="4" t="n"/>
       <c r="V63" s="4" t="n"/>
       <c r="W63" s="4" t="n"/>
-      <c r="X63" s="4" t="n"/>
+      <c r="X63" s="4" t="n">
+        <v>23.58</v>
+      </c>
       <c r="Y63" s="4" t="n"/>
-      <c r="Z63" s="4" t="n">
-        <v>23.58</v>
-      </c>
+      <c r="Z63" s="4" t="n"/>
       <c r="AA63" s="4" t="n"/>
       <c r="AB63" s="4" t="n"/>
       <c r="AC63" s="4" t="n">
@@ -6365,10 +6367,10 @@
       <c r="V65" s="4" t="n"/>
       <c r="W65" s="4" t="n"/>
       <c r="X65" s="4" t="n"/>
-      <c r="Y65" s="4" t="n">
+      <c r="Y65" s="4" t="n"/>
+      <c r="Z65" s="4" t="n">
         <v>31.7</v>
       </c>
-      <c r="Z65" s="4" t="n"/>
       <c r="AA65" s="4" t="n"/>
       <c r="AB65" s="4" t="n">
         <v>31.8</v>
@@ -6449,10 +6451,10 @@
       <c r="V66" s="4" t="n"/>
       <c r="W66" s="4" t="n"/>
       <c r="X66" s="4" t="n"/>
-      <c r="Y66" s="4" t="n">
+      <c r="Y66" s="4" t="n"/>
+      <c r="Z66" s="4" t="n">
         <v>33.9</v>
       </c>
-      <c r="Z66" s="4" t="n"/>
       <c r="AA66" s="4" t="n"/>
       <c r="AB66" s="4" t="n"/>
       <c r="AC66" s="4" t="n"/>
@@ -6528,11 +6530,11 @@
       <c r="U67" s="4" t="n"/>
       <c r="V67" s="4" t="n"/>
       <c r="W67" s="4" t="n"/>
-      <c r="X67" s="4" t="n"/>
+      <c r="X67" s="4" t="n">
+        <v>17.8</v>
+      </c>
       <c r="Y67" s="4" t="n"/>
-      <c r="Z67" s="4" t="n">
-        <v>17.8</v>
-      </c>
+      <c r="Z67" s="4" t="n"/>
       <c r="AA67" s="4" t="n"/>
       <c r="AB67" s="4" t="n"/>
       <c r="AC67" s="4" t="n"/>
@@ -6619,12 +6621,12 @@
       <c r="V68" s="4" t="n"/>
       <c r="W68" s="4" t="n"/>
       <c r="X68" s="4" t="n">
+        <v>27.34</v>
+      </c>
+      <c r="Y68" s="4" t="n">
         <v>28.06</v>
       </c>
-      <c r="Y68" s="4" t="n"/>
-      <c r="Z68" s="4" t="n">
-        <v>27.34</v>
-      </c>
+      <c r="Z68" s="4" t="n"/>
       <c r="AA68" s="4" t="n">
         <v>27.05</v>
       </c>
@@ -7131,10 +7133,10 @@
         <v>33.49</v>
       </c>
       <c r="X74" s="4" t="n"/>
-      <c r="Y74" s="4" t="n">
+      <c r="Y74" s="4" t="n"/>
+      <c r="Z74" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="Z74" s="4" t="n"/>
       <c r="AA74" s="4" t="n"/>
       <c r="AB74" s="4" t="n">
         <v>33.5</v>
@@ -7756,11 +7758,11 @@
       <c r="U82" s="4" t="n"/>
       <c r="V82" s="4" t="n"/>
       <c r="W82" s="4" t="n"/>
-      <c r="X82" s="4" t="n"/>
+      <c r="X82" s="4" t="n">
+        <v>55.6</v>
+      </c>
       <c r="Y82" s="4" t="n"/>
-      <c r="Z82" s="4" t="n">
-        <v>55.6</v>
-      </c>
+      <c r="Z82" s="4" t="n"/>
       <c r="AA82" s="4" t="n"/>
       <c r="AB82" s="4" t="n"/>
       <c r="AC82" s="4" t="n"/>
@@ -8316,22 +8318,22 @@
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
+          <t>速尾★4</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>速尾★6</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
           <t>狼崽★5</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>300+★6</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>速尾★4</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>速尾★6</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
@@ -8901,11 +8903,11 @@
       <c r="AT5" s="4" t="n"/>
       <c r="AU5" s="4" t="n"/>
       <c r="AV5" s="4" t="n"/>
-      <c r="AW5" s="4" t="n"/>
+      <c r="AW5" s="4" t="n">
+        <v>17.96</v>
+      </c>
       <c r="AX5" s="4" t="n"/>
-      <c r="AY5" s="4" t="n">
-        <v>17.96</v>
-      </c>
+      <c r="AY5" s="4" t="n"/>
       <c r="AZ5" s="4" t="n"/>
       <c r="BA5" s="4" t="n"/>
       <c r="BB5" s="4" t="n"/>
@@ -9342,11 +9344,11 @@
       <c r="AS9" s="4" t="n"/>
       <c r="AT9" s="4" t="n"/>
       <c r="AU9" s="4" t="n"/>
-      <c r="AV9" s="4" t="n"/>
+      <c r="AV9" s="4" t="n">
+        <v>20.52</v>
+      </c>
       <c r="AW9" s="4" t="n"/>
-      <c r="AX9" s="4" t="n">
-        <v>20.52</v>
-      </c>
+      <c r="AX9" s="4" t="n"/>
       <c r="AY9" s="4" t="n"/>
       <c r="AZ9" s="4" t="n"/>
       <c r="BA9" s="4" t="n"/>
@@ -9558,11 +9560,11 @@
       <c r="AS11" s="4" t="n"/>
       <c r="AT11" s="4" t="n"/>
       <c r="AU11" s="4" t="n"/>
-      <c r="AV11" s="4" t="n">
+      <c r="AV11" s="4" t="n"/>
+      <c r="AW11" s="4" t="n"/>
+      <c r="AX11" s="4" t="n">
         <v>37.99</v>
       </c>
-      <c r="AW11" s="4" t="n"/>
-      <c r="AX11" s="4" t="n"/>
       <c r="AY11" s="4" t="n"/>
       <c r="AZ11" s="4" t="n"/>
       <c r="BA11" s="4" t="n"/>
@@ -10306,11 +10308,11 @@
       <c r="AS18" s="4" t="n"/>
       <c r="AT18" s="4" t="n"/>
       <c r="AU18" s="4" t="n"/>
-      <c r="AV18" s="4" t="n"/>
+      <c r="AV18" s="4" t="n">
+        <v>24.59</v>
+      </c>
       <c r="AW18" s="4" t="n"/>
-      <c r="AX18" s="4" t="n">
-        <v>24.59</v>
-      </c>
+      <c r="AX18" s="4" t="n"/>
       <c r="AY18" s="4" t="n"/>
       <c r="AZ18" s="4" t="n">
         <v>24.5</v>
@@ -10950,11 +10952,11 @@
       <c r="AS24" s="4" t="n"/>
       <c r="AT24" s="4" t="n"/>
       <c r="AU24" s="4" t="n"/>
-      <c r="AV24" s="4" t="n"/>
+      <c r="AV24" s="4" t="n">
+        <v>23.69</v>
+      </c>
       <c r="AW24" s="4" t="n"/>
-      <c r="AX24" s="4" t="n">
-        <v>23.69</v>
-      </c>
+      <c r="AX24" s="4" t="n"/>
       <c r="AY24" s="4" t="n"/>
       <c r="AZ24" s="4" t="n"/>
       <c r="BA24" s="4" t="n"/>
@@ -11393,11 +11395,11 @@
       <c r="AT28" s="4" t="n"/>
       <c r="AU28" s="4" t="n"/>
       <c r="AV28" s="4" t="n"/>
-      <c r="AW28" s="4" t="n"/>
+      <c r="AW28" s="4" t="n">
+        <v>32.9</v>
+      </c>
       <c r="AX28" s="4" t="n"/>
-      <c r="AY28" s="4" t="n">
-        <v>32.9</v>
-      </c>
+      <c r="AY28" s="4" t="n"/>
       <c r="AZ28" s="4" t="n"/>
       <c r="BA28" s="4" t="n">
         <v>32.6</v>
@@ -11826,14 +11828,14 @@
       <c r="AS32" s="4" t="n"/>
       <c r="AT32" s="4" t="n"/>
       <c r="AU32" s="4" t="n"/>
-      <c r="AV32" s="4" t="n">
+      <c r="AV32" s="4" t="n"/>
+      <c r="AW32" s="4" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="AX32" s="4" t="n">
         <v>29.3</v>
       </c>
-      <c r="AW32" s="4" t="n"/>
-      <c r="AX32" s="4" t="n"/>
-      <c r="AY32" s="4" t="n">
-        <v>28.3</v>
-      </c>
+      <c r="AY32" s="4" t="n"/>
       <c r="AZ32" s="4" t="n"/>
       <c r="BA32" s="4" t="n">
         <v>28.1</v>
@@ -12916,11 +12918,11 @@
       <c r="AS42" s="4" t="n"/>
       <c r="AT42" s="4" t="n"/>
       <c r="AU42" s="4" t="n"/>
-      <c r="AV42" s="4" t="n">
+      <c r="AV42" s="4" t="n"/>
+      <c r="AW42" s="4" t="n"/>
+      <c r="AX42" s="4" t="n">
         <v>22.8</v>
       </c>
-      <c r="AW42" s="4" t="n"/>
-      <c r="AX42" s="4" t="n"/>
       <c r="AY42" s="4" t="n"/>
       <c r="AZ42" s="4" t="n"/>
       <c r="BA42" s="4" t="n">
@@ -13564,11 +13566,11 @@
       <c r="AS48" s="4" t="n"/>
       <c r="AT48" s="4" t="n"/>
       <c r="AU48" s="4" t="n"/>
-      <c r="AV48" s="4" t="n">
+      <c r="AV48" s="4" t="n"/>
+      <c r="AW48" s="4" t="n"/>
+      <c r="AX48" s="4" t="n">
         <v>25.8</v>
       </c>
-      <c r="AW48" s="4" t="n"/>
-      <c r="AX48" s="4" t="n"/>
       <c r="AY48" s="4" t="n"/>
       <c r="AZ48" s="4" t="n"/>
       <c r="BA48" s="4" t="n"/>
@@ -15613,11 +15615,11 @@
       <c r="AT67" s="4" t="n"/>
       <c r="AU67" s="4" t="n"/>
       <c r="AV67" s="4" t="n"/>
-      <c r="AW67" s="4" t="n"/>
+      <c r="AW67" s="4" t="n">
+        <v>18.09</v>
+      </c>
       <c r="AX67" s="4" t="n"/>
-      <c r="AY67" s="4" t="n">
-        <v>18.09</v>
-      </c>
+      <c r="AY67" s="4" t="n"/>
       <c r="AZ67" s="4" t="n"/>
       <c r="BA67" s="4" t="n"/>
       <c r="BB67" s="4" t="n"/>
@@ -15721,11 +15723,11 @@
       <c r="AT68" s="4" t="n"/>
       <c r="AU68" s="4" t="n"/>
       <c r="AV68" s="4" t="n"/>
-      <c r="AW68" s="4" t="n"/>
+      <c r="AW68" s="4" t="n">
+        <v>27.68</v>
+      </c>
       <c r="AX68" s="4" t="n"/>
-      <c r="AY68" s="4" t="n">
-        <v>27.68</v>
-      </c>
+      <c r="AY68" s="4" t="n"/>
       <c r="AZ68" s="4" t="n"/>
       <c r="BA68" s="4" t="n"/>
       <c r="BB68" s="4" t="n"/>
@@ -16472,11 +16474,11 @@
       <c r="AS75" s="4" t="n"/>
       <c r="AT75" s="4" t="n"/>
       <c r="AU75" s="4" t="n"/>
-      <c r="AV75" s="4" t="n">
+      <c r="AV75" s="4" t="n"/>
+      <c r="AW75" s="4" t="n"/>
+      <c r="AX75" s="4" t="n">
         <v>27.5</v>
       </c>
-      <c r="AW75" s="4" t="n"/>
-      <c r="AX75" s="4" t="n"/>
       <c r="AY75" s="4" t="n"/>
       <c r="AZ75" s="4" t="n"/>
       <c r="BA75" s="4" t="n"/>
@@ -17838,22 +17840,22 @@
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
+          <t>速尾★4</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>速尾★6</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
           <t>狼崽★5</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>300+★6</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>速尾★4</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>速尾★6</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
@@ -18268,18 +18270,18 @@
       <c r="AS3" s="4" t="n"/>
       <c r="AT3" s="4" t="n"/>
       <c r="AU3" s="4" t="n"/>
-      <c r="AV3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AW3" s="4" t="n"/>
-      <c r="AX3" s="4" t="n"/>
-      <c r="AY3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV3" s="4" t="n"/>
+      <c r="AW3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AX3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AY3" s="4" t="n"/>
       <c r="AZ3" s="4" t="n"/>
       <c r="BA3" s="4" t="inlineStr">
         <is>
@@ -18410,13 +18412,13 @@
       <c r="AS4" s="4" t="n"/>
       <c r="AT4" s="4" t="n"/>
       <c r="AU4" s="4" t="n"/>
-      <c r="AV4" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV4" s="4" t="n"/>
       <c r="AW4" s="4" t="n"/>
-      <c r="AX4" s="4" t="n"/>
+      <c r="AX4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AY4" s="4" t="n"/>
       <c r="AZ4" s="4" t="n"/>
       <c r="BA4" s="4" t="n"/>
@@ -18565,13 +18567,13 @@
       <c r="AT5" s="4" t="n"/>
       <c r="AU5" s="4" t="n"/>
       <c r="AV5" s="4" t="n"/>
-      <c r="AW5" s="4" t="n"/>
+      <c r="AW5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AX5" s="4" t="n"/>
-      <c r="AY5" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY5" s="4" t="n"/>
       <c r="AZ5" s="4" t="n"/>
       <c r="BA5" s="4" t="inlineStr">
         <is>
@@ -18876,13 +18878,13 @@
       <c r="AS7" s="4" t="n"/>
       <c r="AT7" s="4" t="n"/>
       <c r="AU7" s="4" t="n"/>
-      <c r="AV7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV7" s="4" t="n"/>
       <c r="AW7" s="4" t="n"/>
-      <c r="AX7" s="4" t="n"/>
+      <c r="AX7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AY7" s="4" t="n"/>
       <c r="AZ7" s="4" t="n"/>
       <c r="BA7" s="4" t="n"/>
@@ -19058,18 +19060,18 @@
       <c r="AS8" s="4" t="n"/>
       <c r="AT8" s="4" t="n"/>
       <c r="AU8" s="4" t="n"/>
-      <c r="AV8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AW8" s="4" t="n"/>
-      <c r="AX8" s="4" t="n"/>
-      <c r="AY8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV8" s="4" t="n"/>
+      <c r="AW8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AX8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AY8" s="4" t="n"/>
       <c r="AZ8" s="4" t="n"/>
       <c r="BA8" s="4" t="n"/>
       <c r="BB8" s="4" t="inlineStr">
@@ -19212,13 +19214,13 @@
       <c r="AS9" s="4" t="n"/>
       <c r="AT9" s="4" t="n"/>
       <c r="AU9" s="4" t="n"/>
-      <c r="AV9" s="4" t="n"/>
+      <c r="AV9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW9" s="4" t="n"/>
-      <c r="AX9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AX9" s="4" t="n"/>
       <c r="AY9" s="4" t="n"/>
       <c r="AZ9" s="4" t="n"/>
       <c r="BA9" s="4" t="inlineStr">
@@ -19556,18 +19558,18 @@
       <c r="AS11" s="4" t="n"/>
       <c r="AT11" s="4" t="n"/>
       <c r="AU11" s="4" t="n"/>
-      <c r="AV11" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AW11" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AX11" s="4" t="n"/>
-      <c r="AY11" s="4" t="n"/>
+      <c r="AV11" s="4" t="n"/>
+      <c r="AW11" s="4" t="n"/>
+      <c r="AX11" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AY11" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ11" s="4" t="n"/>
       <c r="BA11" s="4" t="n"/>
       <c r="BB11" s="4" t="inlineStr">
@@ -19710,18 +19712,18 @@
       <c r="AS12" s="4" t="n"/>
       <c r="AT12" s="4" t="n"/>
       <c r="AU12" s="4" t="n"/>
-      <c r="AV12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AW12" s="4" t="n"/>
-      <c r="AX12" s="4" t="n"/>
-      <c r="AY12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV12" s="4" t="n"/>
+      <c r="AW12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AX12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AY12" s="4" t="n"/>
       <c r="AZ12" s="4" t="n"/>
       <c r="BA12" s="4" t="inlineStr">
         <is>
@@ -19872,18 +19874,18 @@
       <c r="AS13" s="4" t="n"/>
       <c r="AT13" s="4" t="n"/>
       <c r="AU13" s="4" t="n"/>
-      <c r="AV13" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AW13" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AX13" s="4" t="n"/>
-      <c r="AY13" s="4" t="n"/>
+      <c r="AV13" s="4" t="n"/>
+      <c r="AW13" s="4" t="n"/>
+      <c r="AX13" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AY13" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ13" s="4" t="n"/>
       <c r="BA13" s="4" t="n"/>
       <c r="BB13" s="4" t="n"/>
@@ -20042,13 +20044,13 @@
       <c r="AS14" s="4" t="n"/>
       <c r="AT14" s="4" t="n"/>
       <c r="AU14" s="4" t="n"/>
-      <c r="AV14" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV14" s="4" t="n"/>
       <c r="AW14" s="4" t="n"/>
-      <c r="AX14" s="4" t="n"/>
+      <c r="AX14" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AY14" s="4" t="n"/>
       <c r="AZ14" s="4" t="n"/>
       <c r="BA14" s="4" t="n"/>
@@ -20200,18 +20202,18 @@
       <c r="AS15" s="4" t="n"/>
       <c r="AT15" s="4" t="n"/>
       <c r="AU15" s="4" t="n"/>
-      <c r="AV15" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AW15" s="4" t="n"/>
-      <c r="AX15" s="4" t="n"/>
-      <c r="AY15" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV15" s="4" t="n"/>
+      <c r="AW15" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AX15" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AY15" s="4" t="n"/>
       <c r="AZ15" s="4" t="n"/>
       <c r="BA15" s="4" t="inlineStr">
         <is>
@@ -20374,13 +20376,13 @@
       <c r="AS16" s="4" t="n"/>
       <c r="AT16" s="4" t="n"/>
       <c r="AU16" s="4" t="n"/>
-      <c r="AV16" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV16" s="4" t="n"/>
       <c r="AW16" s="4" t="n"/>
-      <c r="AX16" s="4" t="n"/>
+      <c r="AX16" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AY16" s="4" t="n"/>
       <c r="AZ16" s="4" t="n"/>
       <c r="BA16" s="4" t="n"/>
@@ -20528,13 +20530,13 @@
       <c r="AS17" s="4" t="n"/>
       <c r="AT17" s="4" t="n"/>
       <c r="AU17" s="4" t="n"/>
-      <c r="AV17" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV17" s="4" t="n"/>
       <c r="AW17" s="4" t="n"/>
-      <c r="AX17" s="4" t="n"/>
+      <c r="AX17" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AY17" s="4" t="n"/>
       <c r="AZ17" s="4" t="n"/>
       <c r="BA17" s="4" t="n"/>
@@ -20679,17 +20681,17 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AW18" s="4" t="n"/>
+      <c r="AW18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AX18" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AY18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY18" s="4" t="n"/>
       <c r="AZ18" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -20848,18 +20850,18 @@
       <c r="AS19" s="4" t="n"/>
       <c r="AT19" s="4" t="n"/>
       <c r="AU19" s="4" t="n"/>
-      <c r="AV19" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AW19" s="4" t="n"/>
-      <c r="AX19" s="4" t="n"/>
-      <c r="AY19" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV19" s="4" t="n"/>
+      <c r="AW19" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AX19" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AY19" s="4" t="n"/>
       <c r="AZ19" s="4" t="n"/>
       <c r="BA19" s="4" t="n"/>
       <c r="BB19" s="4" t="n"/>
@@ -21156,13 +21158,13 @@
       <c r="AS21" s="4" t="n"/>
       <c r="AT21" s="4" t="n"/>
       <c r="AU21" s="4" t="n"/>
-      <c r="AV21" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV21" s="4" t="n"/>
       <c r="AW21" s="4" t="n"/>
-      <c r="AX21" s="4" t="n"/>
+      <c r="AX21" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AY21" s="4" t="n"/>
       <c r="AZ21" s="4" t="n"/>
       <c r="BA21" s="4" t="n"/>
@@ -21318,13 +21320,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AV22" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV22" s="4" t="n"/>
       <c r="AW22" s="4" t="n"/>
-      <c r="AX22" s="4" t="n"/>
+      <c r="AX22" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AY22" s="4" t="n"/>
       <c r="AZ22" s="4" t="n"/>
       <c r="BA22" s="4" t="inlineStr">
@@ -21472,18 +21474,18 @@
       <c r="AS23" s="4" t="n"/>
       <c r="AT23" s="4" t="n"/>
       <c r="AU23" s="4" t="n"/>
-      <c r="AV23" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AW23" s="4" t="n"/>
-      <c r="AX23" s="4" t="n"/>
-      <c r="AY23" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV23" s="4" t="n"/>
+      <c r="AW23" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AX23" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AY23" s="4" t="n"/>
       <c r="AZ23" s="4" t="n"/>
       <c r="BA23" s="4" t="n"/>
       <c r="BB23" s="4" t="n"/>
@@ -21765,13 +21767,13 @@
       <c r="AT25" s="4" t="n"/>
       <c r="AU25" s="4" t="n"/>
       <c r="AV25" s="4" t="n"/>
-      <c r="AW25" s="4" t="n"/>
+      <c r="AW25" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AX25" s="4" t="n"/>
-      <c r="AY25" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY25" s="4" t="n"/>
       <c r="AZ25" s="4" t="n"/>
       <c r="BA25" s="4" t="inlineStr">
         <is>
@@ -21922,13 +21924,13 @@
       <c r="AS26" s="4" t="n"/>
       <c r="AT26" s="4" t="n"/>
       <c r="AU26" s="4" t="n"/>
-      <c r="AV26" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV26" s="4" t="n"/>
       <c r="AW26" s="4" t="n"/>
-      <c r="AX26" s="4" t="n"/>
+      <c r="AX26" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AY26" s="4" t="n"/>
       <c r="AZ26" s="4" t="n"/>
       <c r="BA26" s="4" t="inlineStr">
@@ -22108,13 +22110,13 @@
       <c r="AS27" s="4" t="n"/>
       <c r="AT27" s="4" t="n"/>
       <c r="AU27" s="4" t="n"/>
-      <c r="AV27" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV27" s="4" t="n"/>
       <c r="AW27" s="4" t="n"/>
-      <c r="AX27" s="4" t="n"/>
+      <c r="AX27" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AY27" s="4" t="n"/>
       <c r="AZ27" s="4" t="n"/>
       <c r="BA27" s="4" t="n"/>
@@ -22250,18 +22252,18 @@
       <c r="AS28" s="4" t="n"/>
       <c r="AT28" s="4" t="n"/>
       <c r="AU28" s="4" t="n"/>
-      <c r="AV28" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AW28" s="4" t="n"/>
-      <c r="AX28" s="4" t="n"/>
-      <c r="AY28" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV28" s="4" t="n"/>
+      <c r="AW28" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AX28" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AY28" s="4" t="n"/>
       <c r="AZ28" s="4" t="n"/>
       <c r="BA28" s="4" t="inlineStr">
         <is>
@@ -22408,13 +22410,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AV29" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV29" s="4" t="n"/>
       <c r="AW29" s="4" t="n"/>
-      <c r="AX29" s="4" t="n"/>
+      <c r="AX29" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AY29" s="4" t="n"/>
       <c r="AZ29" s="4" t="n"/>
       <c r="BA29" s="4" t="n"/>
@@ -22854,17 +22856,17 @@
       <c r="AS32" s="4" t="n"/>
       <c r="AT32" s="4" t="n"/>
       <c r="AU32" s="4" t="n"/>
-      <c r="AV32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV32" s="4" t="n"/>
       <c r="AW32" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AX32" s="4" t="n"/>
+      <c r="AX32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AY32" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -23194,18 +23196,18 @@
       <c r="AS34" s="4" t="n"/>
       <c r="AT34" s="4" t="n"/>
       <c r="AU34" s="4" t="n"/>
-      <c r="AV34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AW34" s="4" t="n"/>
-      <c r="AX34" s="4" t="n"/>
-      <c r="AY34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV34" s="4" t="n"/>
+      <c r="AW34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AX34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AY34" s="4" t="n"/>
       <c r="AZ34" s="4" t="n"/>
       <c r="BA34" s="4" t="inlineStr">
         <is>
@@ -23478,18 +23480,18 @@
       <c r="AS36" s="4" t="n"/>
       <c r="AT36" s="4" t="n"/>
       <c r="AU36" s="4" t="n"/>
-      <c r="AV36" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AW36" s="4" t="n"/>
-      <c r="AX36" s="4" t="n"/>
-      <c r="AY36" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV36" s="4" t="n"/>
+      <c r="AW36" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AX36" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AY36" s="4" t="n"/>
       <c r="AZ36" s="4" t="n"/>
       <c r="BA36" s="4" t="n"/>
       <c r="BB36" s="4" t="n"/>
@@ -23787,13 +23789,13 @@
       <c r="AT38" s="4" t="n"/>
       <c r="AU38" s="4" t="n"/>
       <c r="AV38" s="4" t="n"/>
-      <c r="AW38" s="4" t="n"/>
+      <c r="AW38" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AX38" s="4" t="n"/>
-      <c r="AY38" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY38" s="4" t="n"/>
       <c r="AZ38" s="4" t="n"/>
       <c r="BA38" s="4" t="inlineStr">
         <is>
@@ -23944,18 +23946,18 @@
       <c r="AS39" s="4" t="n"/>
       <c r="AT39" s="4" t="n"/>
       <c r="AU39" s="4" t="n"/>
-      <c r="AV39" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AW39" s="4" t="n"/>
-      <c r="AX39" s="4" t="n"/>
-      <c r="AY39" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV39" s="4" t="n"/>
+      <c r="AW39" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AX39" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AY39" s="4" t="n"/>
       <c r="AZ39" s="4" t="n"/>
       <c r="BA39" s="4" t="inlineStr">
         <is>
@@ -24280,18 +24282,18 @@
       <c r="AS41" s="4" t="n"/>
       <c r="AT41" s="4" t="n"/>
       <c r="AU41" s="4" t="n"/>
-      <c r="AV41" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AW41" s="4" t="n"/>
-      <c r="AX41" s="4" t="n"/>
-      <c r="AY41" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV41" s="4" t="n"/>
+      <c r="AW41" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AX41" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AY41" s="4" t="n"/>
       <c r="AZ41" s="4" t="n"/>
       <c r="BA41" s="4" t="n"/>
       <c r="BB41" s="4" t="n"/>
@@ -24442,13 +24444,13 @@
       <c r="AS42" s="4" t="n"/>
       <c r="AT42" s="4" t="n"/>
       <c r="AU42" s="4" t="n"/>
-      <c r="AV42" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV42" s="4" t="n"/>
       <c r="AW42" s="4" t="n"/>
-      <c r="AX42" s="4" t="n"/>
+      <c r="AX42" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AY42" s="4" t="n"/>
       <c r="AZ42" s="4" t="n"/>
       <c r="BA42" s="4" t="inlineStr">
@@ -24600,13 +24602,13 @@
       <c r="AS43" s="4" t="n"/>
       <c r="AT43" s="4" t="n"/>
       <c r="AU43" s="4" t="n"/>
-      <c r="AV43" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV43" s="4" t="n"/>
       <c r="AW43" s="4" t="n"/>
-      <c r="AX43" s="4" t="n"/>
+      <c r="AX43" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AY43" s="4" t="n"/>
       <c r="AZ43" s="4" t="n"/>
       <c r="BA43" s="4" t="inlineStr">
@@ -24916,13 +24918,13 @@
       <c r="AS45" s="4" t="n"/>
       <c r="AT45" s="4" t="n"/>
       <c r="AU45" s="4" t="n"/>
-      <c r="AV45" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV45" s="4" t="n"/>
       <c r="AW45" s="4" t="n"/>
-      <c r="AX45" s="4" t="n"/>
+      <c r="AX45" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AY45" s="4" t="n"/>
       <c r="AZ45" s="4" t="n"/>
       <c r="BA45" s="4" t="n"/>
@@ -25074,13 +25076,13 @@
       <c r="AS46" s="4" t="n"/>
       <c r="AT46" s="4" t="n"/>
       <c r="AU46" s="4" t="n"/>
-      <c r="AV46" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV46" s="4" t="n"/>
       <c r="AW46" s="4" t="n"/>
-      <c r="AX46" s="4" t="n"/>
+      <c r="AX46" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AY46" s="4" t="n"/>
       <c r="AZ46" s="4" t="n"/>
       <c r="BA46" s="4" t="n"/>
@@ -25236,13 +25238,13 @@
       <c r="AS47" s="4" t="n"/>
       <c r="AT47" s="4" t="n"/>
       <c r="AU47" s="4" t="n"/>
-      <c r="AV47" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV47" s="4" t="n"/>
       <c r="AW47" s="4" t="n"/>
-      <c r="AX47" s="4" t="n"/>
+      <c r="AX47" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AY47" s="4" t="n"/>
       <c r="AZ47" s="4" t="n"/>
       <c r="BA47" s="4" t="n"/>
@@ -25394,13 +25396,13 @@
       <c r="AS48" s="4" t="n"/>
       <c r="AT48" s="4" t="n"/>
       <c r="AU48" s="4" t="n"/>
-      <c r="AV48" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV48" s="4" t="n"/>
       <c r="AW48" s="4" t="n"/>
-      <c r="AX48" s="4" t="n"/>
+      <c r="AX48" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AY48" s="4" t="n"/>
       <c r="AZ48" s="4" t="n"/>
       <c r="BA48" s="4" t="n"/>
@@ -25860,13 +25862,13 @@
       <c r="AS51" s="4" t="n"/>
       <c r="AT51" s="4" t="n"/>
       <c r="AU51" s="4" t="n"/>
-      <c r="AV51" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV51" s="4" t="n"/>
       <c r="AW51" s="4" t="n"/>
-      <c r="AX51" s="4" t="n"/>
+      <c r="AX51" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AY51" s="4" t="n"/>
       <c r="AZ51" s="4" t="n"/>
       <c r="BA51" s="4" t="inlineStr">
@@ -26014,13 +26016,13 @@
       <c r="AS52" s="4" t="n"/>
       <c r="AT52" s="4" t="n"/>
       <c r="AU52" s="4" t="n"/>
-      <c r="AV52" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV52" s="4" t="n"/>
       <c r="AW52" s="4" t="n"/>
-      <c r="AX52" s="4" t="n"/>
+      <c r="AX52" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AY52" s="4" t="n"/>
       <c r="AZ52" s="4" t="n"/>
       <c r="BA52" s="4" t="n"/>
@@ -26172,18 +26174,18 @@
       <c r="AS53" s="4" t="n"/>
       <c r="AT53" s="4" t="n"/>
       <c r="AU53" s="4" t="n"/>
-      <c r="AV53" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AW53" s="4" t="n"/>
-      <c r="AX53" s="4" t="n"/>
-      <c r="AY53" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV53" s="4" t="n"/>
+      <c r="AW53" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AX53" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AY53" s="4" t="n"/>
       <c r="AZ53" s="4" t="n"/>
       <c r="BA53" s="4" t="n"/>
       <c r="BB53" s="4" t="n"/>
@@ -26334,13 +26336,13 @@
       <c r="AS54" s="4" t="n"/>
       <c r="AT54" s="4" t="n"/>
       <c r="AU54" s="4" t="n"/>
-      <c r="AV54" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV54" s="4" t="n"/>
       <c r="AW54" s="4" t="n"/>
-      <c r="AX54" s="4" t="n"/>
+      <c r="AX54" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AY54" s="4" t="n"/>
       <c r="AZ54" s="4" t="n"/>
       <c r="BA54" s="4" t="n"/>
@@ -26630,13 +26632,13 @@
       <c r="AS56" s="4" t="n"/>
       <c r="AT56" s="4" t="n"/>
       <c r="AU56" s="4" t="n"/>
-      <c r="AV56" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV56" s="4" t="n"/>
       <c r="AW56" s="4" t="n"/>
-      <c r="AX56" s="4" t="n"/>
+      <c r="AX56" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AY56" s="4" t="n"/>
       <c r="AZ56" s="4" t="n"/>
       <c r="BA56" s="4" t="n"/>
@@ -26796,18 +26798,18 @@
       </c>
       <c r="AT57" s="4" t="n"/>
       <c r="AU57" s="4" t="n"/>
-      <c r="AV57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AW57" s="4" t="n"/>
-      <c r="AX57" s="4" t="n"/>
-      <c r="AY57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV57" s="4" t="n"/>
+      <c r="AW57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AX57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AY57" s="4" t="n"/>
       <c r="AZ57" s="4" t="n"/>
       <c r="BA57" s="4" t="n"/>
       <c r="BB57" s="4" t="n"/>
@@ -26974,13 +26976,13 @@
       <c r="AS58" s="4" t="n"/>
       <c r="AT58" s="4" t="n"/>
       <c r="AU58" s="4" t="n"/>
-      <c r="AV58" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV58" s="4" t="n"/>
       <c r="AW58" s="4" t="n"/>
-      <c r="AX58" s="4" t="n"/>
+      <c r="AX58" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AY58" s="4" t="n"/>
       <c r="AZ58" s="4" t="n"/>
       <c r="BA58" s="4" t="inlineStr">
@@ -27262,13 +27264,13 @@
       <c r="AS60" s="4" t="n"/>
       <c r="AT60" s="4" t="n"/>
       <c r="AU60" s="4" t="n"/>
-      <c r="AV60" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV60" s="4" t="n"/>
       <c r="AW60" s="4" t="n"/>
-      <c r="AX60" s="4" t="n"/>
+      <c r="AX60" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AY60" s="4" t="n"/>
       <c r="AZ60" s="4" t="n"/>
       <c r="BA60" s="4" t="n"/>
@@ -27567,13 +27569,13 @@
       <c r="AT62" s="4" t="n"/>
       <c r="AU62" s="4" t="n"/>
       <c r="AV62" s="4" t="n"/>
-      <c r="AW62" s="4" t="n"/>
+      <c r="AW62" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AX62" s="4" t="n"/>
-      <c r="AY62" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY62" s="4" t="n"/>
       <c r="AZ62" s="4" t="n"/>
       <c r="BA62" s="4" t="inlineStr">
         <is>
@@ -27728,13 +27730,13 @@
       <c r="AS63" s="4" t="n"/>
       <c r="AT63" s="4" t="n"/>
       <c r="AU63" s="4" t="n"/>
-      <c r="AV63" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV63" s="4" t="n"/>
       <c r="AW63" s="4" t="n"/>
-      <c r="AX63" s="4" t="n"/>
+      <c r="AX63" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AY63" s="4" t="n"/>
       <c r="AZ63" s="4" t="n"/>
       <c r="BA63" s="4" t="n"/>
@@ -27890,18 +27892,18 @@
       <c r="AS64" s="4" t="n"/>
       <c r="AT64" s="4" t="n"/>
       <c r="AU64" s="4" t="n"/>
-      <c r="AV64" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AW64" s="4" t="n"/>
-      <c r="AX64" s="4" t="n"/>
-      <c r="AY64" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV64" s="4" t="n"/>
+      <c r="AW64" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AX64" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AY64" s="4" t="n"/>
       <c r="AZ64" s="4" t="n"/>
       <c r="BA64" s="4" t="n"/>
       <c r="BB64" s="4" t="n"/>
@@ -28036,17 +28038,17 @@
       <c r="AS65" s="4" t="n"/>
       <c r="AT65" s="4" t="n"/>
       <c r="AU65" s="4" t="n"/>
-      <c r="AV65" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV65" s="4" t="n"/>
       <c r="AW65" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AX65" s="4" t="n"/>
+      <c r="AX65" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AY65" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -28202,13 +28204,13 @@
       <c r="AS66" s="4" t="n"/>
       <c r="AT66" s="4" t="n"/>
       <c r="AU66" s="4" t="n"/>
-      <c r="AV66" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV66" s="4" t="n"/>
       <c r="AW66" s="4" t="n"/>
-      <c r="AX66" s="4" t="n"/>
+      <c r="AX66" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AY66" s="4" t="n"/>
       <c r="AZ66" s="4" t="n"/>
       <c r="BA66" s="4" t="n"/>
@@ -28341,13 +28343,13 @@
       <c r="AT67" s="4" t="n"/>
       <c r="AU67" s="4" t="n"/>
       <c r="AV67" s="4" t="n"/>
-      <c r="AW67" s="4" t="n"/>
+      <c r="AW67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AX67" s="4" t="n"/>
-      <c r="AY67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY67" s="4" t="n"/>
       <c r="AZ67" s="4" t="n"/>
       <c r="BA67" s="4" t="inlineStr">
         <is>
@@ -28514,18 +28516,18 @@
       <c r="AS68" s="4" t="n"/>
       <c r="AT68" s="4" t="n"/>
       <c r="AU68" s="4" t="n"/>
-      <c r="AV68" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AW68" s="4" t="n"/>
-      <c r="AX68" s="4" t="n"/>
-      <c r="AY68" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV68" s="4" t="n"/>
+      <c r="AW68" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AX68" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AY68" s="4" t="n"/>
       <c r="AZ68" s="4" t="n"/>
       <c r="BA68" s="4" t="inlineStr">
         <is>
@@ -28996,18 +28998,18 @@
       <c r="AS71" s="4" t="n"/>
       <c r="AT71" s="4" t="n"/>
       <c r="AU71" s="4" t="n"/>
-      <c r="AV71" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AW71" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AX71" s="4" t="n"/>
-      <c r="AY71" s="4" t="n"/>
+      <c r="AV71" s="4" t="n"/>
+      <c r="AW71" s="4" t="n"/>
+      <c r="AX71" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AY71" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ71" s="4" t="n"/>
       <c r="BA71" s="4" t="n"/>
       <c r="BB71" s="4" t="n"/>
@@ -29155,13 +29157,13 @@
       <c r="AT72" s="4" t="n"/>
       <c r="AU72" s="4" t="n"/>
       <c r="AV72" s="4" t="n"/>
-      <c r="AW72" s="4" t="n"/>
+      <c r="AW72" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AX72" s="4" t="n"/>
-      <c r="AY72" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY72" s="4" t="n"/>
       <c r="AZ72" s="4" t="n"/>
       <c r="BA72" s="4" t="n"/>
       <c r="BB72" s="4" t="n"/>
@@ -29458,18 +29460,18 @@
       <c r="AS74" s="4" t="n"/>
       <c r="AT74" s="4" t="n"/>
       <c r="AU74" s="4" t="n"/>
-      <c r="AV74" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AW74" s="4" t="n"/>
-      <c r="AX74" s="4" t="n"/>
-      <c r="AY74" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV74" s="4" t="n"/>
+      <c r="AW74" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AX74" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AY74" s="4" t="n"/>
       <c r="AZ74" s="4" t="n"/>
       <c r="BA74" s="4" t="inlineStr">
         <is>
@@ -29620,18 +29622,18 @@
       <c r="AS75" s="4" t="n"/>
       <c r="AT75" s="4" t="n"/>
       <c r="AU75" s="4" t="n"/>
-      <c r="AV75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AW75" s="4" t="n"/>
-      <c r="AX75" s="4" t="n"/>
-      <c r="AY75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV75" s="4" t="n"/>
+      <c r="AW75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AX75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AY75" s="4" t="n"/>
       <c r="AZ75" s="4" t="n"/>
       <c r="BA75" s="4" t="inlineStr">
         <is>
@@ -29940,13 +29942,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AV77" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV77" s="4" t="n"/>
       <c r="AW77" s="4" t="n"/>
-      <c r="AX77" s="4" t="n"/>
+      <c r="AX77" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AY77" s="4" t="n"/>
       <c r="AZ77" s="4" t="n"/>
       <c r="BA77" s="4" t="n"/>
@@ -30094,13 +30096,13 @@
       <c r="AS78" s="4" t="n"/>
       <c r="AT78" s="4" t="n"/>
       <c r="AU78" s="4" t="n"/>
-      <c r="AV78" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV78" s="4" t="n"/>
       <c r="AW78" s="4" t="n"/>
-      <c r="AX78" s="4" t="n"/>
+      <c r="AX78" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AY78" s="4" t="n"/>
       <c r="AZ78" s="4" t="n"/>
       <c r="BA78" s="4" t="n"/>
@@ -30244,13 +30246,13 @@
       <c r="AS79" s="4" t="n"/>
       <c r="AT79" s="4" t="n"/>
       <c r="AU79" s="4" t="n"/>
-      <c r="AV79" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV79" s="4" t="n"/>
       <c r="AW79" s="4" t="n"/>
-      <c r="AX79" s="4" t="n"/>
+      <c r="AX79" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AY79" s="4" t="n"/>
       <c r="AZ79" s="4" t="n"/>
       <c r="BA79" s="4" t="n"/>
@@ -30398,13 +30400,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AV80" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV80" s="4" t="n"/>
       <c r="AW80" s="4" t="n"/>
-      <c r="AX80" s="4" t="n"/>
+      <c r="AX80" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AY80" s="4" t="n"/>
       <c r="AZ80" s="4" t="n"/>
       <c r="BA80" s="4" t="n"/>
@@ -35116,14 +35118,14 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>21c</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>万达</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>21c</t>
-        </is>
-      </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
           <t>狼崽</t>
@@ -35161,14 +35163,14 @@
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
+          <t>复仇</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
           <t>007s</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>复仇</t>
-        </is>
-      </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
           <t>塞纳</t>
@@ -35216,24 +35218,24 @@
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
+          <t>att</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
           <t>统治</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>大超</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>fe3</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>att</t>
-        </is>
-      </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>杰弟</t>
@@ -35266,12 +35268,12 @@
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
+          <t>600lt</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
           <t>5n</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>600lt</t>
         </is>
       </c>
     </row>
@@ -35309,10 +35311,10 @@
       </c>
       <c r="T2" s="4" t="n"/>
       <c r="U2" s="4" t="n"/>
-      <c r="V2" s="4" t="n">
+      <c r="V2" s="4" t="n"/>
+      <c r="W2" s="4" t="n">
         <v>19.29</v>
       </c>
-      <c r="W2" s="4" t="n"/>
       <c r="X2" s="4" t="n"/>
       <c r="Y2" s="4" t="n"/>
       <c r="Z2" s="4" t="n"/>
@@ -35435,10 +35437,10 @@
       <c r="S4" s="4" t="n"/>
       <c r="T4" s="4" t="n"/>
       <c r="U4" s="4" t="n"/>
-      <c r="V4" s="4" t="n"/>
-      <c r="W4" s="4" t="n">
+      <c r="V4" s="4" t="n">
         <v>30.89</v>
       </c>
+      <c r="W4" s="4" t="n"/>
       <c r="X4" s="4" t="n"/>
       <c r="Y4" s="4" t="n"/>
       <c r="Z4" s="4" t="n"/>
@@ -35520,10 +35522,10 @@
       <c r="AF5" s="4" t="n"/>
       <c r="AG5" s="4" t="n"/>
       <c r="AH5" s="4" t="n"/>
-      <c r="AI5" s="4" t="n">
+      <c r="AI5" s="4" t="n"/>
+      <c r="AJ5" s="4" t="n">
         <v>18.17</v>
       </c>
-      <c r="AJ5" s="4" t="n"/>
       <c r="AK5" s="4" t="n">
         <v>17.93</v>
       </c>
@@ -35699,10 +35701,10 @@
       <c r="U8" s="4" t="n">
         <v>27.87</v>
       </c>
-      <c r="V8" s="4" t="n"/>
-      <c r="W8" s="4" t="n">
+      <c r="V8" s="4" t="n">
         <v>28.49</v>
       </c>
+      <c r="W8" s="4" t="n"/>
       <c r="X8" s="4" t="n"/>
       <c r="Y8" s="4" t="n"/>
       <c r="Z8" s="4" t="n"/>
@@ -35748,10 +35750,10 @@
       <c r="L9" s="4" t="n">
         <v>19.55</v>
       </c>
-      <c r="M9" s="4" t="n"/>
-      <c r="N9" s="4" t="n">
+      <c r="M9" s="4" t="n">
         <v>19.47</v>
       </c>
+      <c r="N9" s="4" t="n"/>
       <c r="O9" s="4" t="n"/>
       <c r="P9" s="4" t="n">
         <v>20.19</v>
@@ -35818,10 +35820,10 @@
       <c r="J10" s="4" t="n"/>
       <c r="K10" s="4" t="n"/>
       <c r="L10" s="4" t="n"/>
-      <c r="M10" s="4" t="n"/>
-      <c r="N10" s="4" t="n">
+      <c r="M10" s="4" t="n">
         <v>23.11</v>
       </c>
+      <c r="N10" s="4" t="n"/>
       <c r="O10" s="4" t="n"/>
       <c r="P10" s="4" t="n"/>
       <c r="Q10" s="4" t="n"/>
@@ -35936,10 +35938,10 @@
       <c r="L12" s="4" t="n">
         <v>21.75</v>
       </c>
-      <c r="M12" s="4" t="n"/>
-      <c r="N12" s="4" t="n">
+      <c r="M12" s="4" t="n">
         <v>21.39</v>
       </c>
+      <c r="N12" s="4" t="n"/>
       <c r="O12" s="4" t="n"/>
       <c r="P12" s="4" t="n"/>
       <c r="Q12" s="4" t="n"/>
@@ -36071,10 +36073,10 @@
       <c r="U14" s="4" t="n">
         <v>25.89</v>
       </c>
-      <c r="V14" s="4" t="n"/>
-      <c r="W14" s="4" t="n">
+      <c r="V14" s="4" t="n">
         <v>26.15</v>
       </c>
+      <c r="W14" s="4" t="n"/>
       <c r="X14" s="4" t="n"/>
       <c r="Y14" s="4" t="n"/>
       <c r="Z14" s="4" t="n"/>
@@ -36342,10 +36344,10 @@
         <v>23.99</v>
       </c>
       <c r="AF18" s="4" t="n"/>
-      <c r="AG18" s="4" t="n">
+      <c r="AG18" s="4" t="n"/>
+      <c r="AH18" s="4" t="n">
         <v>23.79</v>
       </c>
-      <c r="AH18" s="4" t="n"/>
       <c r="AI18" s="4" t="n"/>
       <c r="AJ18" s="4" t="n"/>
       <c r="AK18" s="4" t="n"/>
@@ -36438,10 +36440,10 @@
       <c r="J20" s="4" t="n"/>
       <c r="K20" s="4" t="n"/>
       <c r="L20" s="4" t="n"/>
-      <c r="M20" s="4" t="n">
+      <c r="M20" s="4" t="n"/>
+      <c r="N20" s="4" t="n">
         <v>22.59</v>
       </c>
-      <c r="N20" s="4" t="n"/>
       <c r="O20" s="4" t="n"/>
       <c r="P20" s="4" t="n"/>
       <c r="Q20" s="4" t="n"/>
@@ -36449,10 +36451,10 @@
       <c r="S20" s="4" t="n"/>
       <c r="T20" s="4" t="n"/>
       <c r="U20" s="4" t="n"/>
-      <c r="V20" s="4" t="n">
+      <c r="V20" s="4" t="n"/>
+      <c r="W20" s="4" t="n">
         <v>22.79</v>
       </c>
-      <c r="W20" s="4" t="n"/>
       <c r="X20" s="4" t="n"/>
       <c r="Y20" s="4" t="n"/>
       <c r="Z20" s="4" t="n"/>
@@ -36588,10 +36590,10 @@
       <c r="AD22" s="4" t="n"/>
       <c r="AE22" s="4" t="n"/>
       <c r="AF22" s="4" t="n"/>
-      <c r="AG22" s="4" t="n">
+      <c r="AG22" s="4" t="n"/>
+      <c r="AH22" s="4" t="n">
         <v>31.75</v>
       </c>
-      <c r="AH22" s="4" t="n"/>
       <c r="AI22" s="4" t="n"/>
       <c r="AJ22" s="4" t="n"/>
       <c r="AK22" s="4" t="n"/>
@@ -36682,10 +36684,10 @@
       <c r="L24" s="4" t="n">
         <v>22.78</v>
       </c>
-      <c r="M24" s="4" t="n"/>
-      <c r="N24" s="4" t="n">
+      <c r="M24" s="4" t="n">
         <v>22.69</v>
       </c>
+      <c r="N24" s="4" t="n"/>
       <c r="O24" s="4" t="n"/>
       <c r="P24" s="4" t="n"/>
       <c r="Q24" s="4" t="n"/>
@@ -36740,10 +36742,10 @@
       <c r="L25" s="4" t="n">
         <v>24.03</v>
       </c>
-      <c r="M25" s="4" t="n"/>
-      <c r="N25" s="4" t="n">
+      <c r="M25" s="4" t="n">
         <v>24.13</v>
       </c>
+      <c r="N25" s="4" t="n"/>
       <c r="O25" s="4" t="n"/>
       <c r="P25" s="4" t="n"/>
       <c r="Q25" s="4" t="n">
@@ -36764,12 +36766,12 @@
       <c r="AD25" s="4" t="n"/>
       <c r="AE25" s="4" t="n"/>
       <c r="AF25" s="4" t="n"/>
-      <c r="AG25" s="4" t="n"/>
+      <c r="AG25" s="4" t="n">
+        <v>24.22</v>
+      </c>
       <c r="AH25" s="4" t="n"/>
       <c r="AI25" s="4" t="n"/>
-      <c r="AJ25" s="4" t="n">
-        <v>24.22</v>
-      </c>
+      <c r="AJ25" s="4" t="n"/>
       <c r="AK25" s="4" t="n"/>
       <c r="AL25" s="4" t="n"/>
       <c r="AM25" s="4" t="n"/>
@@ -36806,10 +36808,10 @@
       <c r="L26" s="4" t="n">
         <v>18.65</v>
       </c>
-      <c r="M26" s="4" t="n"/>
-      <c r="N26" s="4" t="n">
+      <c r="M26" s="4" t="n">
         <v>18.59</v>
       </c>
+      <c r="N26" s="4" t="n"/>
       <c r="O26" s="4" t="n"/>
       <c r="P26" s="4" t="n"/>
       <c r="Q26" s="4" t="n"/>
@@ -37013,10 +37015,10 @@
       <c r="AE29" s="4" t="n"/>
       <c r="AF29" s="4" t="n"/>
       <c r="AG29" s="4" t="n"/>
-      <c r="AH29" s="4" t="n">
+      <c r="AH29" s="4" t="n"/>
+      <c r="AI29" s="4" t="n">
         <v>18.25</v>
       </c>
-      <c r="AI29" s="4" t="n"/>
       <c r="AJ29" s="4" t="n"/>
       <c r="AK29" s="4" t="n"/>
       <c r="AL29" s="4" t="n"/>
@@ -37050,10 +37052,10 @@
       <c r="J30" s="4" t="n"/>
       <c r="K30" s="4" t="n"/>
       <c r="L30" s="4" t="n"/>
-      <c r="M30" s="4" t="n">
+      <c r="M30" s="4" t="n"/>
+      <c r="N30" s="4" t="n">
         <v>23.29</v>
       </c>
-      <c r="N30" s="4" t="n"/>
       <c r="O30" s="4" t="n"/>
       <c r="P30" s="4" t="n">
         <v>23.39</v>
@@ -37063,10 +37065,10 @@
       <c r="S30" s="4" t="n"/>
       <c r="T30" s="4" t="n"/>
       <c r="U30" s="4" t="n"/>
-      <c r="V30" s="4" t="n">
+      <c r="V30" s="4" t="n"/>
+      <c r="W30" s="4" t="n">
         <v>23.2</v>
       </c>
-      <c r="W30" s="4" t="n"/>
       <c r="X30" s="4" t="n"/>
       <c r="Y30" s="4" t="n"/>
       <c r="Z30" s="4" t="n"/>
@@ -37125,10 +37127,10 @@
       </c>
       <c r="T31" s="4" t="n"/>
       <c r="U31" s="4" t="n"/>
-      <c r="V31" s="4" t="n">
+      <c r="V31" s="4" t="n"/>
+      <c r="W31" s="4" t="n">
         <v>19.29</v>
       </c>
-      <c r="W31" s="4" t="n"/>
       <c r="X31" s="4" t="n"/>
       <c r="Y31" s="4" t="n"/>
       <c r="Z31" s="4" t="n"/>
@@ -37192,10 +37194,10 @@
       <c r="T32" s="4" t="n"/>
       <c r="U32" s="4" t="n"/>
       <c r="V32" s="4" t="n">
+        <v>28.29</v>
+      </c>
+      <c r="W32" s="4" t="n">
         <v>29.03</v>
-      </c>
-      <c r="W32" s="4" t="n">
-        <v>28.29</v>
       </c>
       <c r="X32" s="4" t="n"/>
       <c r="Y32" s="4" t="n"/>
@@ -37210,10 +37212,10 @@
       <c r="AF32" s="4" t="n"/>
       <c r="AG32" s="4" t="n"/>
       <c r="AH32" s="4" t="n"/>
-      <c r="AI32" s="4" t="n">
+      <c r="AI32" s="4" t="n"/>
+      <c r="AJ32" s="4" t="n">
         <v>29.05</v>
       </c>
-      <c r="AJ32" s="4" t="n"/>
       <c r="AK32" s="4" t="n"/>
       <c r="AL32" s="4" t="n"/>
       <c r="AM32" s="4" t="n"/>
@@ -37246,10 +37248,10 @@
       <c r="J33" s="4" t="n"/>
       <c r="K33" s="4" t="n"/>
       <c r="L33" s="4" t="n"/>
-      <c r="M33" s="4" t="n">
+      <c r="M33" s="4" t="n"/>
+      <c r="N33" s="4" t="n">
         <v>20.21</v>
       </c>
-      <c r="N33" s="4" t="n"/>
       <c r="O33" s="4" t="n"/>
       <c r="P33" s="4" t="n">
         <v>20.49</v>
@@ -37259,10 +37261,10 @@
       <c r="S33" s="4" t="n"/>
       <c r="T33" s="4" t="n"/>
       <c r="U33" s="4" t="n"/>
-      <c r="V33" s="4" t="n">
+      <c r="V33" s="4" t="n"/>
+      <c r="W33" s="4" t="n">
         <v>20.15</v>
       </c>
-      <c r="W33" s="4" t="n"/>
       <c r="X33" s="4" t="n"/>
       <c r="Y33" s="4" t="n">
         <v>20.23</v>
@@ -37370,10 +37372,10 @@
       <c r="J35" s="4" t="n"/>
       <c r="K35" s="4" t="n"/>
       <c r="L35" s="4" t="n"/>
-      <c r="M35" s="4" t="n">
+      <c r="M35" s="4" t="n"/>
+      <c r="N35" s="4" t="n">
         <v>23.69</v>
       </c>
-      <c r="N35" s="4" t="n"/>
       <c r="O35" s="4" t="n"/>
       <c r="P35" s="4" t="n"/>
       <c r="Q35" s="4" t="n"/>
@@ -37556,10 +37558,10 @@
       <c r="L38" s="4" t="n">
         <v>20.6</v>
       </c>
-      <c r="M38" s="4" t="n"/>
-      <c r="N38" s="4" t="n">
+      <c r="M38" s="4" t="n">
         <v>20.56</v>
       </c>
+      <c r="N38" s="4" t="n"/>
       <c r="O38" s="4" t="n"/>
       <c r="P38" s="4" t="n"/>
       <c r="Q38" s="4" t="n">
@@ -37802,10 +37804,10 @@
       <c r="L42" s="4" t="n">
         <v>22.05</v>
       </c>
-      <c r="M42" s="4" t="n"/>
-      <c r="N42" s="4" t="n">
+      <c r="M42" s="4" t="n">
         <v>21.95</v>
       </c>
+      <c r="N42" s="4" t="n"/>
       <c r="O42" s="4" t="n">
         <v>22.89</v>
       </c>
@@ -37924,10 +37926,10 @@
       <c r="L44" s="4" t="n">
         <v>22.6</v>
       </c>
-      <c r="M44" s="4" t="n"/>
-      <c r="N44" s="4" t="n">
+      <c r="M44" s="4" t="n">
         <v>22.45</v>
       </c>
+      <c r="N44" s="4" t="n"/>
       <c r="O44" s="4" t="n"/>
       <c r="P44" s="4" t="n">
         <v>22.4</v>
@@ -38007,10 +38009,10 @@
       <c r="S45" s="4" t="n"/>
       <c r="T45" s="4" t="n"/>
       <c r="U45" s="4" t="n"/>
-      <c r="V45" s="4" t="n"/>
-      <c r="W45" s="4" t="n">
+      <c r="V45" s="4" t="n">
         <v>40.29</v>
       </c>
+      <c r="W45" s="4" t="n"/>
       <c r="X45" s="4" t="n"/>
       <c r="Y45" s="4" t="n"/>
       <c r="Z45" s="4" t="n"/>
@@ -38228,10 +38230,10 @@
       <c r="J49" s="4" t="n"/>
       <c r="K49" s="4" t="n"/>
       <c r="L49" s="4" t="n"/>
-      <c r="M49" s="4" t="n">
+      <c r="M49" s="4" t="n"/>
+      <c r="N49" s="4" t="n">
         <v>30.99</v>
       </c>
-      <c r="N49" s="4" t="n"/>
       <c r="O49" s="4" t="n"/>
       <c r="P49" s="4" t="n"/>
       <c r="Q49" s="4" t="n"/>
@@ -38286,10 +38288,10 @@
       <c r="J50" s="4" t="n"/>
       <c r="K50" s="4" t="n"/>
       <c r="L50" s="4" t="n"/>
-      <c r="M50" s="4" t="n">
+      <c r="M50" s="4" t="n"/>
+      <c r="N50" s="4" t="n">
         <v>26.75</v>
       </c>
-      <c r="N50" s="4" t="n"/>
       <c r="O50" s="4" t="n"/>
       <c r="P50" s="4" t="n"/>
       <c r="Q50" s="4" t="n"/>
@@ -38350,10 +38352,10 @@
       <c r="L51" s="4" t="n">
         <v>23.75</v>
       </c>
-      <c r="M51" s="4" t="n"/>
-      <c r="N51" s="4" t="n">
+      <c r="M51" s="4" t="n">
         <v>23.48</v>
       </c>
+      <c r="N51" s="4" t="n"/>
       <c r="O51" s="4" t="n"/>
       <c r="P51" s="4" t="n"/>
       <c r="Q51" s="4" t="n"/>
@@ -38372,12 +38374,12 @@
       <c r="AD51" s="4" t="n"/>
       <c r="AE51" s="4" t="n"/>
       <c r="AF51" s="4" t="n"/>
-      <c r="AG51" s="4" t="n"/>
+      <c r="AG51" s="4" t="n">
+        <v>23.99</v>
+      </c>
       <c r="AH51" s="4" t="n"/>
       <c r="AI51" s="4" t="n"/>
-      <c r="AJ51" s="4" t="n">
-        <v>23.99</v>
-      </c>
+      <c r="AJ51" s="4" t="n"/>
       <c r="AK51" s="4" t="n"/>
       <c r="AL51" s="4" t="n"/>
       <c r="AM51" s="4" t="n"/>
@@ -38493,10 +38495,10 @@
       <c r="AE53" s="4" t="n"/>
       <c r="AF53" s="4" t="n"/>
       <c r="AG53" s="4" t="n"/>
-      <c r="AH53" s="4" t="n">
+      <c r="AH53" s="4" t="n"/>
+      <c r="AI53" s="4" t="n">
         <v>33.99</v>
       </c>
-      <c r="AI53" s="4" t="n"/>
       <c r="AJ53" s="4" t="n"/>
       <c r="AK53" s="4" t="n"/>
       <c r="AL53" s="4" t="n"/>
@@ -38588,10 +38590,10 @@
       <c r="J55" s="4" t="n"/>
       <c r="K55" s="4" t="n"/>
       <c r="L55" s="4" t="n"/>
-      <c r="M55" s="4" t="n">
+      <c r="M55" s="4" t="n"/>
+      <c r="N55" s="4" t="n">
         <v>33.3</v>
       </c>
-      <c r="N55" s="4" t="n"/>
       <c r="O55" s="4" t="n"/>
       <c r="P55" s="4" t="n"/>
       <c r="Q55" s="4" t="n"/>
@@ -38735,10 +38737,10 @@
       <c r="AE57" s="4" t="n"/>
       <c r="AF57" s="4" t="n"/>
       <c r="AG57" s="4" t="n"/>
-      <c r="AH57" s="4" t="n">
+      <c r="AH57" s="4" t="n"/>
+      <c r="AI57" s="4" t="n">
         <v>35.59</v>
       </c>
-      <c r="AI57" s="4" t="n"/>
       <c r="AJ57" s="4" t="n"/>
       <c r="AK57" s="4" t="n"/>
       <c r="AL57" s="4" t="n"/>
@@ -38922,7 +38924,9 @@
       <c r="AN60" s="4" t="n"/>
       <c r="AO60" s="4" t="n"/>
       <c r="AP60" s="4" t="n"/>
-      <c r="AQ60" s="4" t="n"/>
+      <c r="AQ60" s="4" t="n">
+        <v>38.65</v>
+      </c>
       <c r="AR60" s="4" t="n"/>
     </row>
     <row r="61">
@@ -38952,10 +38956,10 @@
       <c r="L61" s="4" t="n">
         <v>21.75</v>
       </c>
-      <c r="M61" s="4" t="n"/>
-      <c r="N61" s="4" t="n">
+      <c r="M61" s="4" t="n">
         <v>21.82</v>
       </c>
+      <c r="N61" s="4" t="n"/>
       <c r="O61" s="4" t="n"/>
       <c r="P61" s="4" t="n"/>
       <c r="Q61" s="4" t="n">
@@ -39155,10 +39159,10 @@
       <c r="S64" s="4" t="n"/>
       <c r="T64" s="4" t="n"/>
       <c r="U64" s="4" t="n"/>
-      <c r="V64" s="4" t="n"/>
-      <c r="W64" s="4" t="n">
+      <c r="V64" s="4" t="n">
         <v>35.19</v>
       </c>
+      <c r="W64" s="4" t="n"/>
       <c r="X64" s="4" t="n"/>
       <c r="Y64" s="4" t="n"/>
       <c r="Z64" s="4" t="n"/>
@@ -39316,10 +39320,10 @@
       <c r="J67" s="4" t="n"/>
       <c r="K67" s="4" t="n"/>
       <c r="L67" s="4" t="n"/>
-      <c r="M67" s="4" t="n"/>
-      <c r="N67" s="4" t="n">
+      <c r="M67" s="4" t="n">
         <v>17.95</v>
       </c>
+      <c r="N67" s="4" t="n"/>
       <c r="O67" s="4" t="n"/>
       <c r="P67" s="4" t="n"/>
       <c r="Q67" s="4" t="n"/>
@@ -39502,10 +39506,10 @@
       <c r="L70" s="4" t="n">
         <v>21.29</v>
       </c>
-      <c r="M70" s="4" t="n"/>
-      <c r="N70" s="4" t="n">
+      <c r="M70" s="4" t="n">
         <v>20.99</v>
       </c>
+      <c r="N70" s="4" t="n"/>
       <c r="O70" s="4" t="n"/>
       <c r="P70" s="4" t="n"/>
       <c r="Q70" s="4" t="n">
@@ -39515,10 +39519,10 @@
       <c r="S70" s="4" t="n"/>
       <c r="T70" s="4" t="n"/>
       <c r="U70" s="4" t="n"/>
-      <c r="V70" s="4" t="n">
+      <c r="V70" s="4" t="n"/>
+      <c r="W70" s="4" t="n">
         <v>21.6</v>
       </c>
-      <c r="W70" s="4" t="n"/>
       <c r="X70" s="4" t="n"/>
       <c r="Y70" s="4" t="n"/>
       <c r="Z70" s="4" t="n"/>
@@ -39628,10 +39632,10 @@
       <c r="L72" s="4" t="n">
         <v>25.79</v>
       </c>
-      <c r="M72" s="4" t="n">
+      <c r="M72" s="4" t="n"/>
+      <c r="N72" s="4" t="n">
         <v>26.1</v>
       </c>
-      <c r="N72" s="4" t="n"/>
       <c r="O72" s="4" t="n"/>
       <c r="P72" s="4" t="n"/>
       <c r="Q72" s="4" t="n"/>
@@ -39694,10 +39698,10 @@
       <c r="J73" s="4" t="n"/>
       <c r="K73" s="4" t="n"/>
       <c r="L73" s="4" t="n"/>
-      <c r="M73" s="4" t="n">
+      <c r="M73" s="4" t="n"/>
+      <c r="N73" s="4" t="n">
         <v>19.4</v>
       </c>
-      <c r="N73" s="4" t="n"/>
       <c r="O73" s="4" t="n"/>
       <c r="P73" s="4" t="n">
         <v>19.39</v>
@@ -39756,10 +39760,10 @@
       </c>
       <c r="K74" s="4" t="n"/>
       <c r="L74" s="4" t="n"/>
-      <c r="M74" s="4" t="n">
+      <c r="M74" s="4" t="n"/>
+      <c r="N74" s="4" t="n">
         <v>35.2</v>
       </c>
-      <c r="N74" s="4" t="n"/>
       <c r="O74" s="4" t="n"/>
       <c r="P74" s="4" t="n"/>
       <c r="Q74" s="4" t="n"/>
@@ -39868,10 +39872,10 @@
       <c r="J76" s="4" t="n"/>
       <c r="K76" s="4" t="n"/>
       <c r="L76" s="4" t="n"/>
-      <c r="M76" s="4" t="n">
+      <c r="M76" s="4" t="n"/>
+      <c r="N76" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="N76" s="4" t="n"/>
       <c r="O76" s="4" t="n"/>
       <c r="P76" s="4" t="n">
         <v>17.09</v>
@@ -40003,10 +40007,10 @@
       <c r="S78" s="4" t="n"/>
       <c r="T78" s="4" t="n"/>
       <c r="U78" s="4" t="n"/>
-      <c r="V78" s="4" t="n"/>
-      <c r="W78" s="4" t="n">
+      <c r="V78" s="4" t="n">
         <v>31.9</v>
       </c>
+      <c r="W78" s="4" t="n"/>
       <c r="X78" s="4" t="n"/>
       <c r="Y78" s="4" t="n"/>
       <c r="Z78" s="4" t="n"/>
@@ -40016,10 +40020,10 @@
       <c r="AD78" s="4" t="n"/>
       <c r="AE78" s="4" t="n"/>
       <c r="AF78" s="4" t="n"/>
-      <c r="AG78" s="4" t="n">
+      <c r="AG78" s="4" t="n"/>
+      <c r="AH78" s="4" t="n">
         <v>32.1</v>
       </c>
-      <c r="AH78" s="4" t="n"/>
       <c r="AI78" s="4" t="n"/>
       <c r="AJ78" s="4" t="n"/>
       <c r="AK78" s="4" t="n"/>
@@ -40042,7 +40046,7 @@
         <v>22.79</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>22.75</v>
+        <v>22.69</v>
       </c>
       <c r="E79" s="4" t="n"/>
       <c r="F79" s="4" t="n">
@@ -40063,7 +40067,9 @@
       <c r="S79" s="4" t="n"/>
       <c r="T79" s="4" t="n"/>
       <c r="U79" s="4" t="n"/>
-      <c r="V79" s="4" t="n"/>
+      <c r="V79" s="4" t="n">
+        <v>23.15</v>
+      </c>
       <c r="W79" s="4" t="n"/>
       <c r="X79" s="4" t="n"/>
       <c r="Y79" s="4" t="n"/>
@@ -40613,24 +40619,24 @@
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
+          <t>21c★1</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>21c★4</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>21c★6</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
           <t>万达★6</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>21c★1</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>21c★4</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>21c★6</t>
-        </is>
-      </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>狼崽★5</t>
@@ -40723,24 +40729,24 @@
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
+          <t>att★6</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
           <t>大超★1</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>大超★3</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>fe3★5</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>att★6</t>
-        </is>
-      </c>
       <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>六子★6</t>
@@ -40768,12 +40774,12 @@
       </c>
       <c r="BH1" s="1" t="inlineStr">
         <is>
+          <t>600lt★5</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
           <t>5n★4</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>600lt★5</t>
         </is>
       </c>
     </row>
@@ -40816,12 +40822,12 @@
       <c r="Z2" s="4" t="n"/>
       <c r="AA2" s="4" t="n"/>
       <c r="AB2" s="4" t="n"/>
-      <c r="AC2" s="4" t="n">
-        <v>19.2</v>
-      </c>
+      <c r="AC2" s="4" t="n"/>
       <c r="AD2" s="4" t="n"/>
       <c r="AE2" s="4" t="n"/>
-      <c r="AF2" s="4" t="n"/>
+      <c r="AF2" s="4" t="n">
+        <v>19.2</v>
+      </c>
       <c r="AG2" s="4" t="n"/>
       <c r="AH2" s="4" t="n">
         <v>19.3</v>
@@ -41544,7 +41550,9 @@
       <c r="L12" s="4" t="n"/>
       <c r="M12" s="4" t="n"/>
       <c r="N12" s="4" t="n"/>
-      <c r="O12" s="4" t="n"/>
+      <c r="O12" s="4" t="n">
+        <v>21.99</v>
+      </c>
       <c r="P12" s="4" t="n"/>
       <c r="Q12" s="4" t="n"/>
       <c r="R12" s="4" t="n"/>
@@ -41556,16 +41564,26 @@
       <c r="X12" s="4" t="n"/>
       <c r="Y12" s="4" t="n"/>
       <c r="Z12" s="4" t="n"/>
-      <c r="AA12" s="4" t="n"/>
-      <c r="AB12" s="4" t="n"/>
+      <c r="AA12" s="4" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="AB12" s="4" t="n">
+        <v>21.89</v>
+      </c>
       <c r="AC12" s="4" t="n"/>
-      <c r="AD12" s="4" t="n"/>
-      <c r="AE12" s="4" t="n"/>
+      <c r="AD12" s="4" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="AE12" s="4" t="n">
+        <v>21.69</v>
+      </c>
       <c r="AF12" s="4" t="n"/>
       <c r="AG12" s="4" t="n"/>
       <c r="AH12" s="4" t="n"/>
       <c r="AI12" s="4" t="n"/>
-      <c r="AJ12" s="4" t="n"/>
+      <c r="AJ12" s="4" t="n">
+        <v>22.1</v>
+      </c>
       <c r="AK12" s="4" t="n"/>
       <c r="AL12" s="4" t="n"/>
       <c r="AM12" s="4" t="n"/>
@@ -41580,7 +41598,9 @@
       <c r="AV12" s="4" t="n"/>
       <c r="AW12" s="4" t="n"/>
       <c r="AX12" s="4" t="n"/>
-      <c r="AY12" s="4" t="n"/>
+      <c r="AY12" s="4" t="n">
+        <v>22.19</v>
+      </c>
       <c r="AZ12" s="4" t="n"/>
       <c r="BA12" s="4" t="n"/>
       <c r="BB12" s="4" t="n"/>
@@ -41791,7 +41811,9 @@
       <c r="AD15" s="4" t="n"/>
       <c r="AE15" s="4" t="n"/>
       <c r="AF15" s="4" t="n"/>
-      <c r="AG15" s="4" t="n"/>
+      <c r="AG15" s="4" t="n">
+        <v>30.4</v>
+      </c>
       <c r="AH15" s="4" t="n"/>
       <c r="AI15" s="4" t="n"/>
       <c r="AJ15" s="4" t="n"/>
@@ -42020,7 +42042,9 @@
       <c r="AD18" s="4" t="n"/>
       <c r="AE18" s="4" t="n"/>
       <c r="AF18" s="4" t="n"/>
-      <c r="AG18" s="4" t="n"/>
+      <c r="AG18" s="4" t="n">
+        <v>24.79</v>
+      </c>
       <c r="AH18" s="4" t="n"/>
       <c r="AI18" s="4" t="n"/>
       <c r="AJ18" s="4" t="n"/>
@@ -42158,12 +42182,12 @@
       <c r="Z20" s="4" t="n"/>
       <c r="AA20" s="4" t="n"/>
       <c r="AB20" s="4" t="n"/>
-      <c r="AC20" s="4" t="n">
-        <v>22.8</v>
-      </c>
+      <c r="AC20" s="4" t="n"/>
       <c r="AD20" s="4" t="n"/>
       <c r="AE20" s="4" t="n"/>
-      <c r="AF20" s="4" t="n"/>
+      <c r="AF20" s="4" t="n">
+        <v>22.85</v>
+      </c>
       <c r="AG20" s="4" t="n"/>
       <c r="AH20" s="4" t="n"/>
       <c r="AI20" s="4" t="n"/>
@@ -42281,7 +42305,9 @@
       <c r="E22" s="4" t="n"/>
       <c r="F22" s="4" t="n"/>
       <c r="G22" s="4" t="n"/>
-      <c r="H22" s="4" t="n"/>
+      <c r="H22" s="4" t="n">
+        <v>32.1</v>
+      </c>
       <c r="I22" s="4" t="n"/>
       <c r="J22" s="4" t="n"/>
       <c r="K22" s="4" t="n"/>
@@ -42580,7 +42606,9 @@
       <c r="N26" s="4" t="n"/>
       <c r="O26" s="4" t="n"/>
       <c r="P26" s="4" t="n"/>
-      <c r="Q26" s="4" t="n"/>
+      <c r="Q26" s="4" t="n">
+        <v>18.99</v>
+      </c>
       <c r="R26" s="4" t="n"/>
       <c r="S26" s="4" t="n"/>
       <c r="T26" s="4" t="n"/>
@@ -42590,13 +42618,21 @@
       <c r="X26" s="4" t="n"/>
       <c r="Y26" s="4" t="n"/>
       <c r="Z26" s="4" t="n"/>
-      <c r="AA26" s="4" t="n"/>
-      <c r="AB26" s="4" t="n"/>
+      <c r="AA26" s="4" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="AB26" s="4" t="n">
+        <v>18.95</v>
+      </c>
       <c r="AC26" s="4" t="n"/>
       <c r="AD26" s="4" t="n"/>
-      <c r="AE26" s="4" t="n"/>
+      <c r="AE26" s="4" t="n">
+        <v>18.9</v>
+      </c>
       <c r="AF26" s="4" t="n"/>
-      <c r="AG26" s="4" t="n"/>
+      <c r="AG26" s="4" t="n">
+        <v>19.5</v>
+      </c>
       <c r="AH26" s="4" t="n"/>
       <c r="AI26" s="4" t="n"/>
       <c r="AJ26" s="4" t="n"/>
@@ -42713,14 +42749,20 @@
       <c r="G28" s="4" t="n"/>
       <c r="H28" s="4" t="n"/>
       <c r="I28" s="4" t="n"/>
-      <c r="J28" s="4" t="n"/>
-      <c r="K28" s="4" t="n"/>
+      <c r="J28" s="4" t="n">
+        <v>33.25</v>
+      </c>
+      <c r="K28" s="4" t="n">
+        <v>33.4</v>
+      </c>
       <c r="L28" s="4" t="n"/>
       <c r="M28" s="4" t="n"/>
       <c r="N28" s="4" t="n"/>
       <c r="O28" s="4" t="n"/>
       <c r="P28" s="4" t="n"/>
-      <c r="Q28" s="4" t="n"/>
+      <c r="Q28" s="4" t="n">
+        <v>33.5</v>
+      </c>
       <c r="R28" s="4" t="n"/>
       <c r="S28" s="4" t="n"/>
       <c r="T28" s="4" t="n"/>
@@ -42730,9 +42772,15 @@
       <c r="X28" s="4" t="n"/>
       <c r="Y28" s="4" t="n"/>
       <c r="Z28" s="4" t="n"/>
-      <c r="AA28" s="4" t="n"/>
-      <c r="AB28" s="4" t="n"/>
-      <c r="AC28" s="4" t="n"/>
+      <c r="AA28" s="4" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="AB28" s="4" t="n">
+        <v>33.19</v>
+      </c>
+      <c r="AC28" s="4" t="n">
+        <v>33.79</v>
+      </c>
       <c r="AD28" s="4" t="n"/>
       <c r="AE28" s="4" t="n"/>
       <c r="AF28" s="4" t="n"/>
@@ -42825,13 +42873,13 @@
       <c r="AV29" s="4" t="n"/>
       <c r="AW29" s="4" t="n"/>
       <c r="AX29" s="4" t="n"/>
-      <c r="AY29" s="4" t="n">
+      <c r="AY29" s="4" t="n"/>
+      <c r="AZ29" s="4" t="n">
         <v>18.6</v>
       </c>
-      <c r="AZ29" s="4" t="n">
+      <c r="BA29" s="4" t="n">
         <v>18.4</v>
       </c>
-      <c r="BA29" s="4" t="n"/>
       <c r="BB29" s="4" t="n"/>
       <c r="BC29" s="4" t="n"/>
       <c r="BD29" s="4" t="n"/>
@@ -42949,12 +42997,12 @@
       <c r="Z31" s="4" t="n"/>
       <c r="AA31" s="4" t="n"/>
       <c r="AB31" s="4" t="n"/>
-      <c r="AC31" s="4" t="n">
-        <v>19.45</v>
-      </c>
+      <c r="AC31" s="4" t="n"/>
       <c r="AD31" s="4" t="n"/>
       <c r="AE31" s="4" t="n"/>
-      <c r="AF31" s="4" t="n"/>
+      <c r="AF31" s="4" t="n">
+        <v>19.45</v>
+      </c>
       <c r="AG31" s="4" t="n"/>
       <c r="AH31" s="4" t="n"/>
       <c r="AI31" s="4" t="n"/>
@@ -43056,10 +43104,10 @@
       </c>
       <c r="AY32" s="4" t="n"/>
       <c r="AZ32" s="4" t="n"/>
-      <c r="BA32" s="4" t="n">
+      <c r="BA32" s="4" t="n"/>
+      <c r="BB32" s="4" t="n">
         <v>29.56</v>
       </c>
-      <c r="BB32" s="4" t="n"/>
       <c r="BC32" s="4" t="n"/>
       <c r="BD32" s="4" t="n"/>
       <c r="BE32" s="4" t="n"/>
@@ -43107,12 +43155,12 @@
       <c r="Z33" s="4" t="n"/>
       <c r="AA33" s="4" t="n"/>
       <c r="AB33" s="4" t="n"/>
-      <c r="AC33" s="4" t="n">
-        <v>20.4</v>
-      </c>
+      <c r="AC33" s="4" t="n"/>
       <c r="AD33" s="4" t="n"/>
       <c r="AE33" s="4" t="n"/>
-      <c r="AF33" s="4" t="n"/>
+      <c r="AF33" s="4" t="n">
+        <v>20.4</v>
+      </c>
       <c r="AG33" s="4" t="n"/>
       <c r="AH33" s="4" t="n">
         <v>20.5</v>
@@ -43477,10 +43525,10 @@
       <c r="AA38" s="4" t="n"/>
       <c r="AB38" s="4" t="n"/>
       <c r="AC38" s="4" t="n"/>
-      <c r="AD38" s="4" t="n"/>
-      <c r="AE38" s="4" t="n">
+      <c r="AD38" s="4" t="n">
         <v>21.1</v>
       </c>
+      <c r="AE38" s="4" t="n"/>
       <c r="AF38" s="4" t="n"/>
       <c r="AG38" s="4" t="n"/>
       <c r="AH38" s="4" t="n"/>
@@ -43632,12 +43680,12 @@
       <c r="Z40" s="4" t="n"/>
       <c r="AA40" s="4" t="n"/>
       <c r="AB40" s="4" t="n"/>
-      <c r="AC40" s="4" t="n">
-        <v>35.4</v>
-      </c>
+      <c r="AC40" s="4" t="n"/>
       <c r="AD40" s="4" t="n"/>
       <c r="AE40" s="4" t="n"/>
-      <c r="AF40" s="4" t="n"/>
+      <c r="AF40" s="4" t="n">
+        <v>35.4</v>
+      </c>
       <c r="AG40" s="4" t="n"/>
       <c r="AH40" s="4" t="n"/>
       <c r="AI40" s="4" t="n"/>
@@ -43932,12 +43980,12 @@
       <c r="Z44" s="4" t="n"/>
       <c r="AA44" s="4" t="n"/>
       <c r="AB44" s="4" t="n"/>
-      <c r="AC44" s="4" t="n">
-        <v>22.6</v>
-      </c>
+      <c r="AC44" s="4" t="n"/>
       <c r="AD44" s="4" t="n"/>
       <c r="AE44" s="4" t="n"/>
-      <c r="AF44" s="4" t="n"/>
+      <c r="AF44" s="4" t="n">
+        <v>22.6</v>
+      </c>
       <c r="AG44" s="4" t="n"/>
       <c r="AH44" s="4" t="n"/>
       <c r="AI44" s="4" t="n"/>
@@ -44765,12 +44813,12 @@
       <c r="Z55" s="4" t="n"/>
       <c r="AA55" s="4" t="n"/>
       <c r="AB55" s="4" t="n"/>
-      <c r="AC55" s="4" t="n">
-        <v>33.29</v>
-      </c>
+      <c r="AC55" s="4" t="n"/>
       <c r="AD55" s="4" t="n"/>
       <c r="AE55" s="4" t="n"/>
-      <c r="AF55" s="4" t="n"/>
+      <c r="AF55" s="4" t="n">
+        <v>33.29</v>
+      </c>
       <c r="AG55" s="4" t="n"/>
       <c r="AH55" s="4" t="n"/>
       <c r="AI55" s="4" t="n"/>
@@ -44943,13 +44991,13 @@
       <c r="AV57" s="4" t="n"/>
       <c r="AW57" s="4" t="n"/>
       <c r="AX57" s="4" t="n"/>
-      <c r="AY57" s="4" t="n">
+      <c r="AY57" s="4" t="n"/>
+      <c r="AZ57" s="4" t="n">
         <v>36.39</v>
       </c>
-      <c r="AZ57" s="4" t="n">
+      <c r="BA57" s="4" t="n">
         <v>35.9</v>
       </c>
-      <c r="BA57" s="4" t="n"/>
       <c r="BB57" s="4" t="n"/>
       <c r="BC57" s="4" t="n"/>
       <c r="BD57" s="4" t="n"/>
@@ -45041,8 +45089,12 @@
       <c r="F59" s="4" t="n"/>
       <c r="G59" s="4" t="n"/>
       <c r="H59" s="4" t="n"/>
-      <c r="I59" s="4" t="n"/>
-      <c r="J59" s="4" t="n"/>
+      <c r="I59" s="4" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="J59" s="4" t="n">
+        <v>21.2</v>
+      </c>
       <c r="K59" s="4" t="n"/>
       <c r="L59" s="4" t="n"/>
       <c r="M59" s="4" t="n"/>
@@ -45073,7 +45125,9 @@
       <c r="AJ59" s="4" t="n"/>
       <c r="AK59" s="4" t="n"/>
       <c r="AL59" s="4" t="n"/>
-      <c r="AM59" s="4" t="n"/>
+      <c r="AM59" s="4" t="n">
+        <v>21.45</v>
+      </c>
       <c r="AN59" s="4" t="n"/>
       <c r="AO59" s="4" t="n"/>
       <c r="AP59" s="4" t="n"/>
@@ -45105,15 +45159,27 @@
         </is>
       </c>
       <c r="C60" s="4" t="n"/>
-      <c r="D60" s="4" t="n"/>
+      <c r="D60" s="4" t="n">
+        <v>36.85</v>
+      </c>
       <c r="E60" s="4" t="n"/>
       <c r="F60" s="4" t="n"/>
       <c r="G60" s="4" t="n"/>
-      <c r="H60" s="4" t="n"/>
-      <c r="I60" s="4" t="n"/>
-      <c r="J60" s="4" t="n"/>
-      <c r="K60" s="4" t="n"/>
-      <c r="L60" s="4" t="n"/>
+      <c r="H60" s="4" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="I60" s="4" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="J60" s="4" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="K60" s="4" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="L60" s="4" t="n">
+        <v>35.7</v>
+      </c>
       <c r="M60" s="4" t="n"/>
       <c r="N60" s="4" t="n"/>
       <c r="O60" s="4" t="n"/>
@@ -45124,7 +45190,9 @@
       <c r="T60" s="4" t="n"/>
       <c r="U60" s="4" t="n"/>
       <c r="V60" s="4" t="n"/>
-      <c r="W60" s="4" t="n"/>
+      <c r="W60" s="4" t="n">
+        <v>37.8</v>
+      </c>
       <c r="X60" s="4" t="n"/>
       <c r="Y60" s="4" t="n"/>
       <c r="Z60" s="4" t="n"/>
@@ -45250,17 +45318,27 @@
       <c r="D62" s="4" t="n"/>
       <c r="E62" s="4" t="n"/>
       <c r="F62" s="4" t="n"/>
-      <c r="G62" s="4" t="n"/>
+      <c r="G62" s="4" t="n">
+        <v>31.2</v>
+      </c>
       <c r="H62" s="4" t="n"/>
       <c r="I62" s="4" t="n"/>
-      <c r="J62" s="4" t="n"/>
+      <c r="J62" s="4" t="n">
+        <v>31</v>
+      </c>
       <c r="K62" s="4" t="n"/>
       <c r="L62" s="4" t="n"/>
-      <c r="M62" s="4" t="n"/>
-      <c r="N62" s="4" t="n"/>
+      <c r="M62" s="4" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="N62" s="4" t="n">
+        <v>31.9</v>
+      </c>
       <c r="O62" s="4" t="n"/>
       <c r="P62" s="4" t="n"/>
-      <c r="Q62" s="4" t="n"/>
+      <c r="Q62" s="4" t="n">
+        <v>31.29</v>
+      </c>
       <c r="R62" s="4" t="n"/>
       <c r="S62" s="4" t="n"/>
       <c r="T62" s="4" t="n"/>
@@ -45317,7 +45395,9 @@
       <c r="D63" s="4" t="n"/>
       <c r="E63" s="4" t="n"/>
       <c r="F63" s="4" t="n"/>
-      <c r="G63" s="4" t="n"/>
+      <c r="G63" s="4" t="n">
+        <v>24.09</v>
+      </c>
       <c r="H63" s="4" t="n"/>
       <c r="I63" s="4" t="n">
         <v>23.89</v>
@@ -45334,7 +45414,9 @@
       <c r="O63" s="4" t="n"/>
       <c r="P63" s="4" t="n"/>
       <c r="Q63" s="4" t="n"/>
-      <c r="R63" s="4" t="n"/>
+      <c r="R63" s="4" t="n">
+        <v>24.39</v>
+      </c>
       <c r="S63" s="4" t="n"/>
       <c r="T63" s="4" t="n">
         <v>23.95</v>
@@ -45856,10 +45938,10 @@
       <c r="AB70" s="4" t="n"/>
       <c r="AC70" s="4" t="n"/>
       <c r="AD70" s="4" t="n"/>
-      <c r="AE70" s="4" t="n"/>
-      <c r="AF70" s="4" t="n">
+      <c r="AE70" s="4" t="n">
         <v>21.19</v>
       </c>
+      <c r="AF70" s="4" t="n"/>
       <c r="AG70" s="4" t="n"/>
       <c r="AH70" s="4" t="n"/>
       <c r="AI70" s="4" t="n"/>
@@ -45998,12 +46080,12 @@
       <c r="Z72" s="4" t="n"/>
       <c r="AA72" s="4" t="n"/>
       <c r="AB72" s="4" t="n"/>
-      <c r="AC72" s="4" t="n">
-        <v>26.25</v>
-      </c>
+      <c r="AC72" s="4" t="n"/>
       <c r="AD72" s="4" t="n"/>
       <c r="AE72" s="4" t="n"/>
-      <c r="AF72" s="4" t="n"/>
+      <c r="AF72" s="4" t="n">
+        <v>26.25</v>
+      </c>
       <c r="AG72" s="4" t="n"/>
       <c r="AH72" s="4" t="n"/>
       <c r="AI72" s="4" t="n"/>
@@ -46024,10 +46106,10 @@
       <c r="AX72" s="4" t="n"/>
       <c r="AY72" s="4" t="n"/>
       <c r="AZ72" s="4" t="n"/>
-      <c r="BA72" s="4" t="n">
+      <c r="BA72" s="4" t="n"/>
+      <c r="BB72" s="4" t="n">
         <v>26.39</v>
       </c>
-      <c r="BB72" s="4" t="n"/>
       <c r="BC72" s="4" t="n"/>
       <c r="BD72" s="4" t="n"/>
       <c r="BE72" s="4" t="n"/>
@@ -46118,22 +46200,34 @@
       <c r="D74" s="4" t="n"/>
       <c r="E74" s="4" t="n"/>
       <c r="F74" s="4" t="n"/>
-      <c r="G74" s="4" t="n"/>
+      <c r="G74" s="4" t="n">
+        <v>34.9</v>
+      </c>
       <c r="H74" s="4" t="n"/>
       <c r="I74" s="4" t="n"/>
-      <c r="J74" s="4" t="n"/>
+      <c r="J74" s="4" t="n">
+        <v>35.8</v>
+      </c>
       <c r="K74" s="4" t="n"/>
       <c r="L74" s="4" t="n"/>
-      <c r="M74" s="4" t="n"/>
+      <c r="M74" s="4" t="n">
+        <v>35.2</v>
+      </c>
       <c r="N74" s="4" t="n"/>
       <c r="O74" s="4" t="n"/>
       <c r="P74" s="4" t="n"/>
-      <c r="Q74" s="4" t="n"/>
+      <c r="Q74" s="4" t="n">
+        <v>34.39</v>
+      </c>
       <c r="R74" s="4" t="n"/>
       <c r="S74" s="4" t="n"/>
       <c r="T74" s="4" t="n"/>
-      <c r="U74" s="4" t="n"/>
-      <c r="V74" s="4" t="n"/>
+      <c r="U74" s="4" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="V74" s="4" t="n">
+        <v>35.35</v>
+      </c>
       <c r="W74" s="4" t="n"/>
       <c r="X74" s="4" t="n"/>
       <c r="Y74" s="4" t="n"/>
@@ -46278,12 +46372,12 @@
       <c r="Z76" s="4" t="n"/>
       <c r="AA76" s="4" t="n"/>
       <c r="AB76" s="4" t="n"/>
-      <c r="AC76" s="4" t="n">
-        <v>17.4</v>
-      </c>
+      <c r="AC76" s="4" t="n"/>
       <c r="AD76" s="4" t="n"/>
       <c r="AE76" s="4" t="n"/>
-      <c r="AF76" s="4" t="n"/>
+      <c r="AF76" s="4" t="n">
+        <v>17.4</v>
+      </c>
       <c r="AG76" s="4" t="n"/>
       <c r="AH76" s="4" t="n">
         <v>17.45</v>
@@ -46331,13 +46425,23 @@
       <c r="D77" s="4" t="n"/>
       <c r="E77" s="4" t="n"/>
       <c r="F77" s="4" t="n"/>
-      <c r="G77" s="4" t="n"/>
+      <c r="G77" s="4" t="n">
+        <v>29</v>
+      </c>
       <c r="H77" s="4" t="n"/>
       <c r="I77" s="4" t="n"/>
-      <c r="J77" s="4" t="n"/>
-      <c r="K77" s="4" t="n"/>
-      <c r="L77" s="4" t="n"/>
-      <c r="M77" s="4" t="n"/>
+      <c r="J77" s="4" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="K77" s="4" t="n">
+        <v>29.65</v>
+      </c>
+      <c r="L77" s="4" t="n">
+        <v>29.49</v>
+      </c>
+      <c r="M77" s="4" t="n">
+        <v>29.1</v>
+      </c>
       <c r="N77" s="4" t="n"/>
       <c r="O77" s="4" t="n"/>
       <c r="P77" s="4" t="n"/>
@@ -46401,24 +46505,32 @@
       <c r="E78" s="4" t="n"/>
       <c r="F78" s="4" t="n"/>
       <c r="G78" s="4" t="n">
-        <v>31.05</v>
+        <v>31.15</v>
       </c>
       <c r="H78" s="4" t="n"/>
       <c r="I78" s="4" t="n"/>
-      <c r="J78" s="4" t="n"/>
+      <c r="J78" s="4" t="n">
+        <v>31.55</v>
+      </c>
       <c r="K78" s="4" t="n"/>
       <c r="L78" s="4" t="n"/>
-      <c r="M78" s="4" t="n"/>
+      <c r="M78" s="4" t="n">
+        <v>31.6</v>
+      </c>
       <c r="N78" s="4" t="n"/>
       <c r="O78" s="4" t="n"/>
       <c r="P78" s="4" t="n"/>
       <c r="Q78" s="4" t="n"/>
       <c r="R78" s="4" t="n"/>
-      <c r="S78" s="4" t="n"/>
+      <c r="S78" s="4" t="n">
+        <v>32.2</v>
+      </c>
       <c r="T78" s="4" t="n"/>
       <c r="U78" s="4" t="n"/>
       <c r="V78" s="4" t="n"/>
-      <c r="W78" s="4" t="n"/>
+      <c r="W78" s="4" t="n">
+        <v>32.4</v>
+      </c>
       <c r="X78" s="4" t="n"/>
       <c r="Y78" s="4" t="n"/>
       <c r="Z78" s="4" t="n"/>
@@ -46437,7 +46549,9 @@
       <c r="AM78" s="4" t="n"/>
       <c r="AN78" s="4" t="n"/>
       <c r="AO78" s="4" t="n"/>
-      <c r="AP78" s="4" t="n"/>
+      <c r="AP78" s="4" t="n">
+        <v>32.45</v>
+      </c>
       <c r="AQ78" s="4" t="n"/>
       <c r="AR78" s="4" t="n"/>
       <c r="AS78" s="4" t="n"/>
@@ -46469,19 +46583,27 @@
       <c r="D79" s="4" t="n"/>
       <c r="E79" s="4" t="n"/>
       <c r="F79" s="4" t="n"/>
-      <c r="G79" s="4" t="n"/>
+      <c r="G79" s="4" t="n">
+        <v>22.99</v>
+      </c>
       <c r="H79" s="4" t="n"/>
       <c r="I79" s="4" t="n"/>
-      <c r="J79" s="4" t="n"/>
+      <c r="J79" s="4" t="n">
+        <v>22.9</v>
+      </c>
       <c r="K79" s="4" t="n"/>
       <c r="L79" s="4" t="n"/>
-      <c r="M79" s="4" t="n"/>
+      <c r="M79" s="4" t="n">
+        <v>23.2</v>
+      </c>
       <c r="N79" s="4" t="n"/>
       <c r="O79" s="4" t="n"/>
       <c r="P79" s="4" t="n"/>
       <c r="Q79" s="4" t="n"/>
       <c r="R79" s="4" t="n"/>
-      <c r="S79" s="4" t="n"/>
+      <c r="S79" s="4" t="n">
+        <v>23.3</v>
+      </c>
       <c r="T79" s="4" t="n"/>
       <c r="U79" s="4" t="n"/>
       <c r="V79" s="4" t="n"/>
@@ -46506,7 +46628,9 @@
       <c r="AM79" s="4" t="n"/>
       <c r="AN79" s="4" t="n"/>
       <c r="AO79" s="4" t="n"/>
-      <c r="AP79" s="4" t="n"/>
+      <c r="AP79" s="4" t="n">
+        <v>23.39</v>
+      </c>
       <c r="AQ79" s="4" t="n"/>
       <c r="AR79" s="4" t="n"/>
       <c r="AS79" s="4" t="n"/>
@@ -46864,10 +46988,10 @@
       <c r="Z84" s="4" t="n"/>
       <c r="AA84" s="4" t="n"/>
       <c r="AB84" s="4" t="n"/>
-      <c r="AC84" s="4" t="n"/>
-      <c r="AD84" s="4" t="n">
+      <c r="AC84" s="4" t="n">
         <v>29.43</v>
       </c>
+      <c r="AD84" s="4" t="n"/>
       <c r="AE84" s="4" t="n"/>
       <c r="AF84" s="4" t="n"/>
       <c r="AG84" s="4" t="n"/>
@@ -47144,24 +47268,24 @@
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
+          <t>21c★1</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>21c★4</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>21c★6</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
           <t>万达★6</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>21c★1</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>21c★4</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>21c★6</t>
-        </is>
-      </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>狼崽★5</t>
@@ -47254,24 +47378,24 @@
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
+          <t>att★6</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
           <t>大超★1</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>大超★3</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>fe3★5</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>att★6</t>
-        </is>
-      </c>
       <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>六子★6</t>
@@ -47299,12 +47423,12 @@
       </c>
       <c r="BH1" s="1" t="inlineStr">
         <is>
+          <t>600lt★5</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
           <t>5n★4</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>600lt★5</t>
         </is>
       </c>
     </row>
@@ -47349,14 +47473,14 @@
       <c r="Z2" s="4" t="n"/>
       <c r="AA2" s="4" t="n"/>
       <c r="AB2" s="4" t="n"/>
-      <c r="AC2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AC2" s="4" t="n"/>
       <c r="AD2" s="4" t="n"/>
       <c r="AE2" s="4" t="n"/>
-      <c r="AF2" s="4" t="n"/>
+      <c r="AF2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AG2" s="4" t="n"/>
       <c r="AH2" s="4" t="inlineStr">
         <is>
@@ -47404,12 +47528,12 @@
       <c r="BE2" s="4" t="n"/>
       <c r="BF2" s="4" t="n"/>
       <c r="BG2" s="4" t="n"/>
-      <c r="BH2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI2" s="4" t="n"/>
+      <c r="BH2" s="4" t="n"/>
+      <c r="BI2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n"/>
@@ -47769,14 +47893,14 @@
       <c r="Z6" s="4" t="n"/>
       <c r="AA6" s="4" t="n"/>
       <c r="AB6" s="4" t="n"/>
-      <c r="AC6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AC6" s="4" t="n"/>
       <c r="AD6" s="4" t="n"/>
       <c r="AE6" s="4" t="n"/>
-      <c r="AF6" s="4" t="n"/>
+      <c r="AF6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AG6" s="4" t="n"/>
       <c r="AH6" s="4" t="inlineStr">
         <is>
@@ -47820,12 +47944,12 @@
       <c r="BE6" s="4" t="n"/>
       <c r="BF6" s="4" t="n"/>
       <c r="BG6" s="4" t="n"/>
-      <c r="BH6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI6" s="4" t="n"/>
+      <c r="BH6" s="4" t="n"/>
+      <c r="BI6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
@@ -48120,12 +48244,12 @@
       </c>
       <c r="AC9" s="4" t="n"/>
       <c r="AD9" s="4" t="n"/>
-      <c r="AE9" s="4" t="n"/>
-      <c r="AF9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AE9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AF9" s="4" t="n"/>
       <c r="AG9" s="4" t="n"/>
       <c r="AH9" s="4" t="inlineStr">
         <is>
@@ -48177,12 +48301,12 @@
       <c r="BE9" s="4" t="n"/>
       <c r="BF9" s="4" t="n"/>
       <c r="BG9" s="4" t="n"/>
-      <c r="BH9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI9" s="4" t="n"/>
+      <c r="BH9" s="4" t="n"/>
+      <c r="BI9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -48229,13 +48353,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AC10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AC10" s="4" t="n"/>
       <c r="AD10" s="4" t="n"/>
-      <c r="AE10" s="4" t="n"/>
+      <c r="AE10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF10" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -48417,7 +48541,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="O12" s="4" t="n"/>
+      <c r="O12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P12" s="4" t="n"/>
       <c r="Q12" s="4" t="inlineStr">
         <is>
@@ -48444,13 +48572,17 @@
         </is>
       </c>
       <c r="AC12" s="4" t="n"/>
-      <c r="AD12" s="4" t="n"/>
-      <c r="AE12" s="4" t="n"/>
-      <c r="AF12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AD12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AE12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AF12" s="4" t="n"/>
       <c r="AG12" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -48462,7 +48594,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AJ12" s="4" t="n"/>
+      <c r="AJ12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AK12" s="4" t="n"/>
       <c r="AL12" s="4" t="n"/>
       <c r="AM12" s="4" t="n"/>
@@ -48481,14 +48617,14 @@
       <c r="AV12" s="4" t="n"/>
       <c r="AW12" s="4" t="n"/>
       <c r="AX12" s="4" t="n"/>
-      <c r="AY12" s="4" t="n"/>
+      <c r="AY12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ12" s="4" t="n"/>
       <c r="BA12" s="4" t="n"/>
-      <c r="BB12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BB12" s="4" t="n"/>
       <c r="BC12" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -48667,12 +48803,12 @@
       </c>
       <c r="AC14" s="4" t="n"/>
       <c r="AD14" s="4" t="n"/>
-      <c r="AE14" s="4" t="n"/>
-      <c r="AF14" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AE14" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AF14" s="4" t="n"/>
       <c r="AG14" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -48780,14 +48916,14 @@
         </is>
       </c>
       <c r="AB15" s="4" t="n"/>
-      <c r="AC15" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AC15" s="4" t="n"/>
       <c r="AD15" s="4" t="n"/>
       <c r="AE15" s="4" t="n"/>
-      <c r="AF15" s="4" t="n"/>
+      <c r="AF15" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AG15" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -49006,14 +49142,14 @@
       <c r="Z17" s="4" t="n"/>
       <c r="AA17" s="4" t="n"/>
       <c r="AB17" s="4" t="n"/>
-      <c r="AC17" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AC17" s="4" t="n"/>
       <c r="AD17" s="4" t="n"/>
       <c r="AE17" s="4" t="n"/>
-      <c r="AF17" s="4" t="n"/>
+      <c r="AF17" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AG17" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -49127,12 +49263,12 @@
       </c>
       <c r="AC18" s="4" t="n"/>
       <c r="AD18" s="4" t="n"/>
-      <c r="AE18" s="4" t="n"/>
-      <c r="AF18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AE18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AF18" s="4" t="n"/>
       <c r="AG18" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -49167,14 +49303,14 @@
       <c r="AV18" s="4" t="n"/>
       <c r="AW18" s="4" t="n"/>
       <c r="AX18" s="4" t="n"/>
-      <c r="AY18" s="4" t="n"/>
+      <c r="AY18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ18" s="4" t="n"/>
       <c r="BA18" s="4" t="n"/>
-      <c r="BB18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BB18" s="4" t="n"/>
       <c r="BC18" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -49335,14 +49471,14 @@
       <c r="Z20" s="4" t="n"/>
       <c r="AA20" s="4" t="n"/>
       <c r="AB20" s="4" t="n"/>
-      <c r="AC20" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AC20" s="4" t="n"/>
       <c r="AD20" s="4" t="n"/>
       <c r="AE20" s="4" t="n"/>
-      <c r="AF20" s="4" t="n"/>
+      <c r="AF20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AG20" s="4" t="n"/>
       <c r="AH20" s="4" t="n"/>
       <c r="AI20" s="4" t="n"/>
@@ -49390,12 +49526,12 @@
       <c r="BE20" s="4" t="n"/>
       <c r="BF20" s="4" t="n"/>
       <c r="BG20" s="4" t="n"/>
-      <c r="BH20" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI20" s="4" t="n"/>
+      <c r="BH20" s="4" t="n"/>
+      <c r="BI20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n"/>
@@ -49512,7 +49648,11 @@
       <c r="E22" s="4" t="n"/>
       <c r="F22" s="4" t="n"/>
       <c r="G22" s="4" t="n"/>
-      <c r="H22" s="4" t="n"/>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="I22" s="4" t="n"/>
       <c r="J22" s="4" t="n"/>
       <c r="K22" s="4" t="n"/>
@@ -49757,12 +49897,12 @@
       </c>
       <c r="AC24" s="4" t="n"/>
       <c r="AD24" s="4" t="n"/>
-      <c r="AE24" s="4" t="n"/>
-      <c r="AF24" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AE24" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AF24" s="4" t="n"/>
       <c r="AG24" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -49860,12 +50000,12 @@
       </c>
       <c r="AC25" s="4" t="n"/>
       <c r="AD25" s="4" t="n"/>
-      <c r="AE25" s="4" t="n"/>
-      <c r="AF25" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AE25" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AF25" s="4" t="n"/>
       <c r="AG25" s="4" t="n"/>
       <c r="AH25" s="4" t="n"/>
       <c r="AI25" s="4" t="inlineStr">
@@ -49896,25 +50036,25 @@
       <c r="AV25" s="4" t="n"/>
       <c r="AW25" s="4" t="n"/>
       <c r="AX25" s="4" t="n"/>
-      <c r="AY25" s="4" t="n"/>
+      <c r="AY25" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ25" s="4" t="n"/>
       <c r="BA25" s="4" t="n"/>
-      <c r="BB25" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BB25" s="4" t="n"/>
       <c r="BC25" s="4" t="n"/>
       <c r="BD25" s="4" t="n"/>
       <c r="BE25" s="4" t="n"/>
       <c r="BF25" s="4" t="n"/>
       <c r="BG25" s="4" t="n"/>
-      <c r="BH25" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI25" s="4" t="n"/>
+      <c r="BH25" s="4" t="n"/>
+      <c r="BI25" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -49945,7 +50085,11 @@
       </c>
       <c r="O26" s="4" t="n"/>
       <c r="P26" s="4" t="n"/>
-      <c r="Q26" s="4" t="n"/>
+      <c r="Q26" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="R26" s="4" t="n"/>
       <c r="S26" s="4" t="n"/>
       <c r="T26" s="4" t="n"/>
@@ -49965,13 +50109,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AC26" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AC26" s="4" t="n"/>
       <c r="AD26" s="4" t="n"/>
-      <c r="AE26" s="4" t="n"/>
+      <c r="AE26" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF26" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -50019,14 +50163,14 @@
         </is>
       </c>
       <c r="AX26" s="4" t="n"/>
-      <c r="AY26" s="4" t="n"/>
+      <c r="AY26" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ26" s="4" t="n"/>
       <c r="BA26" s="4" t="n"/>
-      <c r="BB26" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BB26" s="4" t="n"/>
       <c r="BC26" s="4" t="n"/>
       <c r="BD26" s="4" t="n"/>
       <c r="BE26" s="4" t="n"/>
@@ -50152,8 +50296,16 @@
       <c r="G28" s="4" t="n"/>
       <c r="H28" s="4" t="n"/>
       <c r="I28" s="4" t="n"/>
-      <c r="J28" s="4" t="n"/>
-      <c r="K28" s="4" t="n"/>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="L28" s="4" t="n"/>
       <c r="M28" s="4" t="n"/>
       <c r="N28" s="4" t="n"/>
@@ -50183,14 +50335,18 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AC28" s="4" t="n"/>
+      <c r="AC28" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD28" s="4" t="n"/>
-      <c r="AE28" s="4" t="n"/>
-      <c r="AF28" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AE28" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AF28" s="4" t="n"/>
       <c r="AG28" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -50316,17 +50472,17 @@
       <c r="AV29" s="4" t="n"/>
       <c r="AW29" s="4" t="n"/>
       <c r="AX29" s="4" t="n"/>
-      <c r="AY29" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY29" s="4" t="n"/>
       <c r="AZ29" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="BA29" s="4" t="n"/>
+      <c r="BA29" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB29" s="4" t="n"/>
       <c r="BC29" s="4" t="n"/>
       <c r="BD29" s="4" t="n"/>
@@ -50377,14 +50533,14 @@
       <c r="Z30" s="4" t="n"/>
       <c r="AA30" s="4" t="n"/>
       <c r="AB30" s="4" t="n"/>
-      <c r="AC30" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AC30" s="4" t="n"/>
       <c r="AD30" s="4" t="n"/>
       <c r="AE30" s="4" t="n"/>
-      <c r="AF30" s="4" t="n"/>
+      <c r="AF30" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AG30" s="4" t="n"/>
       <c r="AH30" s="4" t="n"/>
       <c r="AI30" s="4" t="n"/>
@@ -50432,12 +50588,12 @@
       <c r="BE30" s="4" t="n"/>
       <c r="BF30" s="4" t="n"/>
       <c r="BG30" s="4" t="n"/>
-      <c r="BH30" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI30" s="4" t="n"/>
+      <c r="BH30" s="4" t="n"/>
+      <c r="BI30" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n"/>
@@ -50476,14 +50632,14 @@
       <c r="Z31" s="4" t="n"/>
       <c r="AA31" s="4" t="n"/>
       <c r="AB31" s="4" t="n"/>
-      <c r="AC31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AC31" s="4" t="n"/>
       <c r="AD31" s="4" t="n"/>
       <c r="AE31" s="4" t="n"/>
-      <c r="AF31" s="4" t="n"/>
+      <c r="AF31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AG31" s="4" t="n"/>
       <c r="AH31" s="4" t="inlineStr">
         <is>
@@ -50526,14 +50682,14 @@
       <c r="AV31" s="4" t="n"/>
       <c r="AW31" s="4" t="n"/>
       <c r="AX31" s="4" t="n"/>
-      <c r="AY31" s="4" t="n"/>
+      <c r="AY31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ31" s="4" t="n"/>
       <c r="BA31" s="4" t="n"/>
-      <c r="BB31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BB31" s="4" t="n"/>
       <c r="BC31" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -50543,12 +50699,12 @@
       <c r="BE31" s="4" t="n"/>
       <c r="BF31" s="4" t="n"/>
       <c r="BG31" s="4" t="n"/>
-      <c r="BH31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI31" s="4" t="n"/>
+      <c r="BH31" s="4" t="n"/>
+      <c r="BI31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n"/>
@@ -50643,12 +50799,12 @@
       </c>
       <c r="AY32" s="4" t="n"/>
       <c r="AZ32" s="4" t="n"/>
-      <c r="BA32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BB32" s="4" t="n"/>
+      <c r="BA32" s="4" t="n"/>
+      <c r="BB32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC32" s="4" t="n"/>
       <c r="BD32" s="4" t="n"/>
       <c r="BE32" s="4" t="n"/>
@@ -50658,12 +50814,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="BH32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI32" s="4" t="n"/>
+      <c r="BH32" s="4" t="n"/>
+      <c r="BI32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -50706,14 +50862,14 @@
       <c r="Z33" s="4" t="n"/>
       <c r="AA33" s="4" t="n"/>
       <c r="AB33" s="4" t="n"/>
-      <c r="AC33" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AC33" s="4" t="n"/>
       <c r="AD33" s="4" t="n"/>
       <c r="AE33" s="4" t="n"/>
-      <c r="AF33" s="4" t="n"/>
+      <c r="AF33" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AG33" s="4" t="n"/>
       <c r="AH33" s="4" t="inlineStr">
         <is>
@@ -50754,23 +50910,23 @@
       <c r="AX33" s="4" t="n"/>
       <c r="AY33" s="4" t="n"/>
       <c r="AZ33" s="4" t="n"/>
-      <c r="BA33" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BB33" s="4" t="n"/>
+      <c r="BA33" s="4" t="n"/>
+      <c r="BB33" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC33" s="4" t="n"/>
       <c r="BD33" s="4" t="n"/>
       <c r="BE33" s="4" t="n"/>
       <c r="BF33" s="4" t="n"/>
       <c r="BG33" s="4" t="n"/>
-      <c r="BH33" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI33" s="4" t="n"/>
+      <c r="BH33" s="4" t="n"/>
+      <c r="BI33" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n"/>
@@ -50863,25 +51019,25 @@
       <c r="AV34" s="4" t="n"/>
       <c r="AW34" s="4" t="n"/>
       <c r="AX34" s="4" t="n"/>
-      <c r="AY34" s="4" t="n"/>
+      <c r="AY34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ34" s="4" t="n"/>
       <c r="BA34" s="4" t="n"/>
-      <c r="BB34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BB34" s="4" t="n"/>
       <c r="BC34" s="4" t="n"/>
       <c r="BD34" s="4" t="n"/>
       <c r="BE34" s="4" t="n"/>
       <c r="BF34" s="4" t="n"/>
       <c r="BG34" s="4" t="n"/>
-      <c r="BH34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI34" s="4" t="n"/>
+      <c r="BH34" s="4" t="n"/>
+      <c r="BI34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n"/>
@@ -50920,14 +51076,14 @@
       <c r="Z35" s="4" t="n"/>
       <c r="AA35" s="4" t="n"/>
       <c r="AB35" s="4" t="n"/>
-      <c r="AC35" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AC35" s="4" t="n"/>
       <c r="AD35" s="4" t="n"/>
       <c r="AE35" s="4" t="n"/>
-      <c r="AF35" s="4" t="n"/>
+      <c r="AF35" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AG35" s="4" t="n"/>
       <c r="AH35" s="4" t="inlineStr">
         <is>
@@ -50968,23 +51124,23 @@
       <c r="AX35" s="4" t="n"/>
       <c r="AY35" s="4" t="n"/>
       <c r="AZ35" s="4" t="n"/>
-      <c r="BA35" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BB35" s="4" t="n"/>
+      <c r="BA35" s="4" t="n"/>
+      <c r="BB35" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC35" s="4" t="n"/>
       <c r="BD35" s="4" t="n"/>
       <c r="BE35" s="4" t="n"/>
       <c r="BF35" s="4" t="n"/>
       <c r="BG35" s="4" t="n"/>
-      <c r="BH35" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI35" s="4" t="n"/>
+      <c r="BH35" s="4" t="n"/>
+      <c r="BI35" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n"/>
@@ -51209,12 +51365,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="BH37" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI37" s="4" t="n"/>
+      <c r="BH37" s="4" t="n"/>
+      <c r="BI37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n"/>
@@ -51266,17 +51422,17 @@
         </is>
       </c>
       <c r="AC38" s="4" t="n"/>
-      <c r="AD38" s="4" t="n"/>
+      <c r="AD38" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AE38" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AF38" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AF38" s="4" t="n"/>
       <c r="AG38" s="4" t="n"/>
       <c r="AH38" s="4" t="n"/>
       <c r="AI38" s="4" t="inlineStr">
@@ -51378,12 +51534,12 @@
       </c>
       <c r="AC39" s="4" t="n"/>
       <c r="AD39" s="4" t="n"/>
-      <c r="AE39" s="4" t="n"/>
-      <c r="AF39" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AE39" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AF39" s="4" t="n"/>
       <c r="AG39" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -51507,14 +51663,14 @@
       <c r="Z40" s="4" t="n"/>
       <c r="AA40" s="4" t="n"/>
       <c r="AB40" s="4" t="n"/>
-      <c r="AC40" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AC40" s="4" t="n"/>
       <c r="AD40" s="4" t="n"/>
       <c r="AE40" s="4" t="n"/>
-      <c r="AF40" s="4" t="n"/>
+      <c r="AF40" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AG40" s="4" t="n"/>
       <c r="AH40" s="4" t="n"/>
       <c r="AI40" s="4" t="n"/>
@@ -51719,12 +51875,12 @@
       </c>
       <c r="AC42" s="4" t="n"/>
       <c r="AD42" s="4" t="n"/>
-      <c r="AE42" s="4" t="n"/>
-      <c r="AF42" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AE42" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AF42" s="4" t="n"/>
       <c r="AG42" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -51911,14 +52067,14 @@
       <c r="Z44" s="4" t="n"/>
       <c r="AA44" s="4" t="n"/>
       <c r="AB44" s="4" t="n"/>
-      <c r="AC44" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AC44" s="4" t="n"/>
       <c r="AD44" s="4" t="n"/>
       <c r="AE44" s="4" t="n"/>
-      <c r="AF44" s="4" t="n"/>
+      <c r="AF44" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AG44" s="4" t="n"/>
       <c r="AH44" s="4" t="inlineStr">
         <is>
@@ -52316,12 +52472,12 @@
       <c r="AX47" s="4" t="n"/>
       <c r="AY47" s="4" t="n"/>
       <c r="AZ47" s="4" t="n"/>
-      <c r="BA47" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BB47" s="4" t="n"/>
+      <c r="BA47" s="4" t="n"/>
+      <c r="BB47" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC47" s="4" t="n"/>
       <c r="BD47" s="4" t="n"/>
       <c r="BE47" s="4" t="n"/>
@@ -52498,14 +52654,14 @@
       <c r="Z49" s="4" t="n"/>
       <c r="AA49" s="4" t="n"/>
       <c r="AB49" s="4" t="n"/>
-      <c r="AC49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AC49" s="4" t="n"/>
       <c r="AD49" s="4" t="n"/>
       <c r="AE49" s="4" t="n"/>
-      <c r="AF49" s="4" t="n"/>
+      <c r="AF49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AG49" s="4" t="n"/>
       <c r="AH49" s="4" t="n"/>
       <c r="AI49" s="4" t="n"/>
@@ -52553,12 +52709,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="BH49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI49" s="4" t="n"/>
+      <c r="BH49" s="4" t="n"/>
+      <c r="BI49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="n"/>
@@ -52597,14 +52753,14 @@
       <c r="Z50" s="4" t="n"/>
       <c r="AA50" s="4" t="n"/>
       <c r="AB50" s="4" t="n"/>
-      <c r="AC50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AC50" s="4" t="n"/>
       <c r="AD50" s="4" t="n"/>
       <c r="AE50" s="4" t="n"/>
-      <c r="AF50" s="4" t="n"/>
+      <c r="AF50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AG50" s="4" t="n"/>
       <c r="AH50" s="4" t="n"/>
       <c r="AI50" s="4" t="n"/>
@@ -52637,12 +52793,12 @@
       <c r="AX50" s="4" t="n"/>
       <c r="AY50" s="4" t="n"/>
       <c r="AZ50" s="4" t="n"/>
-      <c r="BA50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BB50" s="4" t="n"/>
+      <c r="BA50" s="4" t="n"/>
+      <c r="BB50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC50" s="4" t="n"/>
       <c r="BD50" s="4" t="n"/>
       <c r="BE50" s="4" t="inlineStr">
@@ -52652,12 +52808,12 @@
       </c>
       <c r="BF50" s="4" t="n"/>
       <c r="BG50" s="4" t="n"/>
-      <c r="BH50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI50" s="4" t="n"/>
+      <c r="BH50" s="4" t="n"/>
+      <c r="BI50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n"/>
@@ -52706,12 +52862,12 @@
       </c>
       <c r="AC51" s="4" t="n"/>
       <c r="AD51" s="4" t="n"/>
-      <c r="AE51" s="4" t="n"/>
-      <c r="AF51" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AE51" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AF51" s="4" t="n"/>
       <c r="AG51" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -53076,12 +53232,12 @@
       <c r="AW54" s="4" t="n"/>
       <c r="AX54" s="4" t="n"/>
       <c r="AY54" s="4" t="n"/>
-      <c r="AZ54" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BA54" s="4" t="n"/>
+      <c r="AZ54" s="4" t="n"/>
+      <c r="BA54" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB54" s="4" t="n"/>
       <c r="BC54" s="4" t="n"/>
       <c r="BD54" s="4" t="n"/>
@@ -53128,14 +53284,14 @@
       <c r="Z55" s="4" t="n"/>
       <c r="AA55" s="4" t="n"/>
       <c r="AB55" s="4" t="n"/>
-      <c r="AC55" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AC55" s="4" t="n"/>
       <c r="AD55" s="4" t="n"/>
       <c r="AE55" s="4" t="n"/>
-      <c r="AF55" s="4" t="n"/>
+      <c r="AF55" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AG55" s="4" t="n"/>
       <c r="AH55" s="4" t="n"/>
       <c r="AI55" s="4" t="n"/>
@@ -53172,23 +53328,23 @@
       <c r="AX55" s="4" t="n"/>
       <c r="AY55" s="4" t="n"/>
       <c r="AZ55" s="4" t="n"/>
-      <c r="BA55" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BB55" s="4" t="n"/>
+      <c r="BA55" s="4" t="n"/>
+      <c r="BB55" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC55" s="4" t="n"/>
       <c r="BD55" s="4" t="n"/>
       <c r="BE55" s="4" t="n"/>
       <c r="BF55" s="4" t="n"/>
       <c r="BG55" s="4" t="n"/>
-      <c r="BH55" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI55" s="4" t="n"/>
+      <c r="BH55" s="4" t="n"/>
+      <c r="BI55" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n"/>
@@ -53392,17 +53548,17 @@
       <c r="AV57" s="4" t="n"/>
       <c r="AW57" s="4" t="n"/>
       <c r="AX57" s="4" t="n"/>
-      <c r="AY57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY57" s="4" t="n"/>
       <c r="AZ57" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="BA57" s="4" t="n"/>
+      <c r="BA57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB57" s="4" t="n"/>
       <c r="BC57" s="4" t="n"/>
       <c r="BD57" s="4" t="n"/>
@@ -53520,8 +53676,16 @@
       <c r="F59" s="4" t="n"/>
       <c r="G59" s="4" t="n"/>
       <c r="H59" s="4" t="n"/>
-      <c r="I59" s="4" t="n"/>
-      <c r="J59" s="4" t="n"/>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="K59" s="4" t="n"/>
       <c r="L59" s="4" t="n"/>
       <c r="M59" s="4" t="n"/>
@@ -53544,14 +53708,14 @@
       <c r="Z59" s="4" t="n"/>
       <c r="AA59" s="4" t="n"/>
       <c r="AB59" s="4" t="n"/>
-      <c r="AC59" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AC59" s="4" t="n"/>
       <c r="AD59" s="4" t="n"/>
       <c r="AE59" s="4" t="n"/>
-      <c r="AF59" s="4" t="n"/>
+      <c r="AF59" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AG59" s="4" t="n"/>
       <c r="AH59" s="4" t="n"/>
       <c r="AI59" s="4" t="inlineStr">
@@ -53610,7 +53774,11 @@
         </is>
       </c>
       <c r="C60" s="4" t="n"/>
-      <c r="D60" s="4" t="n"/>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="E60" s="4" t="n"/>
       <c r="F60" s="4" t="n"/>
       <c r="G60" s="4" t="inlineStr">
@@ -53618,11 +53786,31 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H60" s="4" t="n"/>
-      <c r="I60" s="4" t="n"/>
-      <c r="J60" s="4" t="n"/>
-      <c r="K60" s="4" t="n"/>
-      <c r="L60" s="4" t="n"/>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K60" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L60" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M60" s="4" t="n"/>
       <c r="N60" s="4" t="n"/>
       <c r="O60" s="4" t="n"/>
@@ -53633,7 +53821,11 @@
       <c r="T60" s="4" t="n"/>
       <c r="U60" s="4" t="n"/>
       <c r="V60" s="4" t="n"/>
-      <c r="W60" s="4" t="n"/>
+      <c r="W60" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="X60" s="4" t="n"/>
       <c r="Y60" s="4" t="n"/>
       <c r="Z60" s="4" t="n"/>
@@ -53738,13 +53930,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AC61" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AC61" s="4" t="n"/>
       <c r="AD61" s="4" t="n"/>
-      <c r="AE61" s="4" t="n"/>
+      <c r="AE61" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF61" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -53819,13 +54011,25 @@
       <c r="D62" s="4" t="n"/>
       <c r="E62" s="4" t="n"/>
       <c r="F62" s="4" t="n"/>
-      <c r="G62" s="4" t="n"/>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H62" s="4" t="n"/>
       <c r="I62" s="4" t="n"/>
-      <c r="J62" s="4" t="n"/>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="K62" s="4" t="n"/>
       <c r="L62" s="4" t="n"/>
-      <c r="M62" s="4" t="n"/>
+      <c r="M62" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N62" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -53853,14 +54057,14 @@
         </is>
       </c>
       <c r="AB62" s="4" t="n"/>
-      <c r="AC62" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AC62" s="4" t="n"/>
       <c r="AD62" s="4" t="n"/>
       <c r="AE62" s="4" t="n"/>
-      <c r="AF62" s="4" t="n"/>
+      <c r="AF62" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AG62" s="4" t="n"/>
       <c r="AH62" s="4" t="n"/>
       <c r="AI62" s="4" t="n"/>
@@ -53900,12 +54104,12 @@
       <c r="BE62" s="4" t="n"/>
       <c r="BF62" s="4" t="n"/>
       <c r="BG62" s="4" t="n"/>
-      <c r="BH62" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI62" s="4" t="n"/>
+      <c r="BH62" s="4" t="n"/>
+      <c r="BI62" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n"/>
@@ -53949,7 +54153,11 @@
       <c r="O63" s="4" t="n"/>
       <c r="P63" s="4" t="n"/>
       <c r="Q63" s="4" t="n"/>
-      <c r="R63" s="4" t="n"/>
+      <c r="R63" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="S63" s="4" t="n"/>
       <c r="T63" s="4" t="inlineStr">
         <is>
@@ -53968,14 +54176,14 @@
       <c r="Z63" s="4" t="n"/>
       <c r="AA63" s="4" t="n"/>
       <c r="AB63" s="4" t="n"/>
-      <c r="AC63" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AC63" s="4" t="n"/>
       <c r="AD63" s="4" t="n"/>
       <c r="AE63" s="4" t="n"/>
-      <c r="AF63" s="4" t="n"/>
+      <c r="AF63" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AG63" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -54228,14 +54436,14 @@
       <c r="AV65" s="4" t="n"/>
       <c r="AW65" s="4" t="n"/>
       <c r="AX65" s="4" t="n"/>
-      <c r="AY65" s="4" t="n"/>
+      <c r="AY65" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ65" s="4" t="n"/>
       <c r="BA65" s="4" t="n"/>
-      <c r="BB65" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BB65" s="4" t="n"/>
       <c r="BC65" s="4" t="n"/>
       <c r="BD65" s="4" t="n"/>
       <c r="BE65" s="4" t="n"/>
@@ -54398,12 +54606,12 @@
       </c>
       <c r="AC67" s="4" t="n"/>
       <c r="AD67" s="4" t="n"/>
-      <c r="AE67" s="4" t="n"/>
-      <c r="AF67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AE67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AF67" s="4" t="n"/>
       <c r="AG67" s="4" t="n"/>
       <c r="AH67" s="4" t="inlineStr">
         <is>
@@ -54452,12 +54660,12 @@
       </c>
       <c r="AY67" s="4" t="n"/>
       <c r="AZ67" s="4" t="n"/>
-      <c r="BA67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BB67" s="4" t="n"/>
+      <c r="BA67" s="4" t="n"/>
+      <c r="BB67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC67" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -54553,14 +54761,14 @@
       <c r="AV68" s="4" t="n"/>
       <c r="AW68" s="4" t="n"/>
       <c r="AX68" s="4" t="n"/>
-      <c r="AY68" s="4" t="n"/>
+      <c r="AY68" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ68" s="4" t="n"/>
       <c r="BA68" s="4" t="n"/>
-      <c r="BB68" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BB68" s="4" t="n"/>
       <c r="BC68" s="4" t="n"/>
       <c r="BD68" s="4" t="n"/>
       <c r="BE68" s="4" t="n"/>
@@ -54715,12 +54923,12 @@
       </c>
       <c r="AC70" s="4" t="n"/>
       <c r="AD70" s="4" t="n"/>
-      <c r="AE70" s="4" t="n"/>
-      <c r="AF70" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AE70" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AF70" s="4" t="n"/>
       <c r="AG70" s="4" t="n"/>
       <c r="AH70" s="4" t="n"/>
       <c r="AI70" s="4" t="inlineStr">
@@ -54911,14 +55119,14 @@
       <c r="Z72" s="4" t="n"/>
       <c r="AA72" s="4" t="n"/>
       <c r="AB72" s="4" t="n"/>
-      <c r="AC72" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AC72" s="4" t="n"/>
       <c r="AD72" s="4" t="n"/>
       <c r="AE72" s="4" t="n"/>
-      <c r="AF72" s="4" t="n"/>
+      <c r="AF72" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AG72" s="4" t="n"/>
       <c r="AH72" s="4" t="inlineStr">
         <is>
@@ -54959,12 +55167,12 @@
       <c r="AX72" s="4" t="n"/>
       <c r="AY72" s="4" t="n"/>
       <c r="AZ72" s="4" t="n"/>
-      <c r="BA72" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BB72" s="4" t="n"/>
+      <c r="BA72" s="4" t="n"/>
+      <c r="BB72" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC72" s="4" t="n"/>
       <c r="BD72" s="4" t="n"/>
       <c r="BE72" s="4" t="n"/>
@@ -55073,12 +55281,12 @@
       <c r="BE73" s="4" t="n"/>
       <c r="BF73" s="4" t="n"/>
       <c r="BG73" s="4" t="n"/>
-      <c r="BH73" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI73" s="4" t="n"/>
+      <c r="BH73" s="4" t="n"/>
+      <c r="BI73" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="n"/>
@@ -55098,10 +55306,18 @@
       </c>
       <c r="H74" s="4" t="n"/>
       <c r="I74" s="4" t="n"/>
-      <c r="J74" s="4" t="n"/>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="K74" s="4" t="n"/>
       <c r="L74" s="4" t="n"/>
-      <c r="M74" s="4" t="n"/>
+      <c r="M74" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N74" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -55117,8 +55333,16 @@
       <c r="R74" s="4" t="n"/>
       <c r="S74" s="4" t="n"/>
       <c r="T74" s="4" t="n"/>
-      <c r="U74" s="4" t="n"/>
-      <c r="V74" s="4" t="n"/>
+      <c r="U74" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V74" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="W74" s="4" t="n"/>
       <c r="X74" s="4" t="n"/>
       <c r="Y74" s="4" t="n"/>
@@ -55129,14 +55353,14 @@
         </is>
       </c>
       <c r="AB74" s="4" t="n"/>
-      <c r="AC74" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AC74" s="4" t="n"/>
       <c r="AD74" s="4" t="n"/>
       <c r="AE74" s="4" t="n"/>
-      <c r="AF74" s="4" t="n"/>
+      <c r="AF74" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AG74" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -55226,12 +55450,12 @@
       </c>
       <c r="AC75" s="4" t="n"/>
       <c r="AD75" s="4" t="n"/>
-      <c r="AE75" s="4" t="n"/>
-      <c r="AF75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AE75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AF75" s="4" t="n"/>
       <c r="AG75" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -55319,14 +55543,14 @@
       <c r="Z76" s="4" t="n"/>
       <c r="AA76" s="4" t="n"/>
       <c r="AB76" s="4" t="n"/>
-      <c r="AC76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AC76" s="4" t="n"/>
       <c r="AD76" s="4" t="n"/>
       <c r="AE76" s="4" t="n"/>
-      <c r="AF76" s="4" t="n"/>
+      <c r="AF76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AG76" s="4" t="n"/>
       <c r="AH76" s="4" t="inlineStr">
         <is>
@@ -55359,12 +55583,12 @@
       <c r="AX76" s="4" t="n"/>
       <c r="AY76" s="4" t="n"/>
       <c r="AZ76" s="4" t="n"/>
-      <c r="BA76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BB76" s="4" t="n"/>
+      <c r="BA76" s="4" t="n"/>
+      <c r="BB76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC76" s="4" t="n"/>
       <c r="BD76" s="4" t="n"/>
       <c r="BE76" s="4" t="inlineStr">
@@ -55407,10 +55631,26 @@
       </c>
       <c r="H77" s="4" t="n"/>
       <c r="I77" s="4" t="n"/>
-      <c r="J77" s="4" t="n"/>
-      <c r="K77" s="4" t="n"/>
-      <c r="L77" s="4" t="n"/>
-      <c r="M77" s="4" t="n"/>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K77" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L77" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M77" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N77" s="4" t="n"/>
       <c r="O77" s="4" t="n"/>
       <c r="P77" s="4" t="n"/>
@@ -55498,20 +55738,36 @@
       </c>
       <c r="H78" s="4" t="n"/>
       <c r="I78" s="4" t="n"/>
-      <c r="J78" s="4" t="n"/>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="K78" s="4" t="n"/>
       <c r="L78" s="4" t="n"/>
-      <c r="M78" s="4" t="n"/>
+      <c r="M78" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N78" s="4" t="n"/>
       <c r="O78" s="4" t="n"/>
       <c r="P78" s="4" t="n"/>
       <c r="Q78" s="4" t="n"/>
       <c r="R78" s="4" t="n"/>
-      <c r="S78" s="4" t="n"/>
+      <c r="S78" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="T78" s="4" t="n"/>
       <c r="U78" s="4" t="n"/>
       <c r="V78" s="4" t="n"/>
-      <c r="W78" s="4" t="n"/>
+      <c r="W78" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="X78" s="4" t="n"/>
       <c r="Y78" s="4" t="n"/>
       <c r="Z78" s="4" t="n"/>
@@ -55542,7 +55798,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AP78" s="4" t="n"/>
+      <c r="AP78" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ78" s="4" t="n"/>
       <c r="AR78" s="4" t="n"/>
       <c r="AS78" s="4" t="n"/>
@@ -55585,16 +55845,28 @@
       </c>
       <c r="H79" s="4" t="n"/>
       <c r="I79" s="4" t="n"/>
-      <c r="J79" s="4" t="n"/>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="K79" s="4" t="n"/>
       <c r="L79" s="4" t="n"/>
-      <c r="M79" s="4" t="n"/>
+      <c r="M79" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N79" s="4" t="n"/>
       <c r="O79" s="4" t="n"/>
       <c r="P79" s="4" t="n"/>
       <c r="Q79" s="4" t="n"/>
       <c r="R79" s="4" t="n"/>
-      <c r="S79" s="4" t="n"/>
+      <c r="S79" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="T79" s="4" t="n"/>
       <c r="U79" s="4" t="n"/>
       <c r="V79" s="4" t="n"/>
@@ -55633,7 +55905,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AP79" s="4" t="n"/>
+      <c r="AP79" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ79" s="4" t="n"/>
       <c r="AR79" s="4" t="n"/>
       <c r="AS79" s="4" t="n"/>
@@ -55746,12 +56022,12 @@
       <c r="AW80" s="4" t="n"/>
       <c r="AX80" s="4" t="n"/>
       <c r="AY80" s="4" t="n"/>
-      <c r="AZ80" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BA80" s="4" t="n"/>
+      <c r="AZ80" s="4" t="n"/>
+      <c r="BA80" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB80" s="4" t="n"/>
       <c r="BC80" s="4" t="n"/>
       <c r="BD80" s="4" t="n"/>
@@ -56063,12 +56339,12 @@
       <c r="Z84" s="4" t="n"/>
       <c r="AA84" s="4" t="n"/>
       <c r="AB84" s="4" t="n"/>
-      <c r="AC84" s="4" t="n"/>
-      <c r="AD84" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AC84" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AD84" s="4" t="n"/>
       <c r="AE84" s="4" t="n"/>
       <c r="AF84" s="4" t="n"/>
       <c r="AG84" s="4" t="n"/>
@@ -56199,12 +56475,12 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>21c</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>万达</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>21c</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -56263,12 +56539,12 @@
       <c r="E2" s="4" t="n"/>
       <c r="F2" s="4" t="n"/>
       <c r="G2" s="4" t="n"/>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="n"/>
+      <c r="H2" s="4" t="n"/>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -56407,12 +56683,12 @@
       <c r="E6" s="4" t="n"/>
       <c r="F6" s="4" t="n"/>
       <c r="G6" s="4" t="n"/>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="n"/>
+      <c r="H6" s="4" t="n"/>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -56513,12 +56789,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H9" s="4" t="n"/>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="n"/>
       <c r="J9" s="4" t="n"/>
       <c r="K9" s="4" t="inlineStr">
         <is>
@@ -56643,12 +56919,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H12" s="4" t="n"/>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="n"/>
       <c r="J12" s="4" t="n"/>
       <c r="K12" s="4" t="n"/>
       <c r="L12" s="4" t="n"/>
@@ -56715,12 +56991,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H14" s="4" t="n"/>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="n"/>
       <c r="J14" s="4" t="n"/>
       <c r="K14" s="4" t="n"/>
       <c r="L14" s="4" t="n"/>
@@ -56749,12 +57025,12 @@
       </c>
       <c r="F15" s="4" t="n"/>
       <c r="G15" s="4" t="n"/>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="n"/>
+      <c r="H15" s="4" t="n"/>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J15" s="4" t="n"/>
       <c r="K15" s="4" t="n"/>
       <c r="L15" s="4" t="inlineStr">
@@ -56813,12 +57089,12 @@
         </is>
       </c>
       <c r="G17" s="4" t="n"/>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="n"/>
+      <c r="H17" s="4" t="n"/>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -56863,12 +57139,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H18" s="4" t="n"/>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="n"/>
       <c r="J18" s="4" t="n"/>
       <c r="K18" s="4" t="n"/>
       <c r="L18" s="4" t="n"/>
@@ -56935,12 +57211,12 @@
       <c r="E20" s="4" t="n"/>
       <c r="F20" s="4" t="n"/>
       <c r="G20" s="4" t="n"/>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I20" s="4" t="n"/>
+      <c r="H20" s="4" t="n"/>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -57071,12 +57347,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H24" s="4" t="n"/>
-      <c r="I24" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="n"/>
       <c r="J24" s="4" t="n"/>
       <c r="K24" s="4" t="inlineStr">
         <is>
@@ -57109,12 +57385,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H25" s="4" t="n"/>
-      <c r="I25" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="n"/>
       <c r="J25" s="4" t="n"/>
       <c r="K25" s="4" t="n"/>
       <c r="L25" s="4" t="n"/>
@@ -57219,12 +57495,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H28" s="4" t="n"/>
-      <c r="I28" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="n"/>
       <c r="J28" s="4" t="n"/>
       <c r="K28" s="4" t="n"/>
       <c r="L28" s="4" t="n"/>
@@ -57283,12 +57559,12 @@
       <c r="E30" s="4" t="n"/>
       <c r="F30" s="4" t="n"/>
       <c r="G30" s="4" t="n"/>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I30" s="4" t="n"/>
+      <c r="H30" s="4" t="n"/>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -57397,12 +57673,12 @@
       <c r="E33" s="4" t="n"/>
       <c r="F33" s="4" t="n"/>
       <c r="G33" s="4" t="n"/>
-      <c r="H33" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I33" s="4" t="n"/>
+      <c r="H33" s="4" t="n"/>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -57465,12 +57741,12 @@
       <c r="E35" s="4" t="n"/>
       <c r="F35" s="4" t="n"/>
       <c r="G35" s="4" t="n"/>
-      <c r="H35" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I35" s="4" t="n"/>
+      <c r="H35" s="4" t="n"/>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J35" s="4" t="n"/>
       <c r="K35" s="4" t="inlineStr">
         <is>
@@ -57583,12 +57859,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H38" s="4" t="n"/>
-      <c r="I38" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="n"/>
       <c r="J38" s="4" t="n"/>
       <c r="K38" s="4" t="inlineStr">
         <is>
@@ -57621,12 +57897,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H39" s="4" t="n"/>
-      <c r="I39" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="n"/>
       <c r="J39" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -57727,12 +58003,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H42" s="4" t="n"/>
-      <c r="I42" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="n"/>
       <c r="J42" s="4" t="n"/>
       <c r="K42" s="4" t="inlineStr">
         <is>
@@ -57791,12 +58067,12 @@
       <c r="E44" s="4" t="n"/>
       <c r="F44" s="4" t="n"/>
       <c r="G44" s="4" t="n"/>
-      <c r="H44" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I44" s="4" t="n"/>
+      <c r="H44" s="4" t="n"/>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -57965,12 +58241,12 @@
       <c r="E49" s="4" t="n"/>
       <c r="F49" s="4" t="n"/>
       <c r="G49" s="4" t="n"/>
-      <c r="H49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I49" s="4" t="n"/>
+      <c r="H49" s="4" t="n"/>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J49" s="4" t="n"/>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -58003,12 +58279,12 @@
       <c r="E50" s="4" t="n"/>
       <c r="F50" s="4" t="n"/>
       <c r="G50" s="4" t="n"/>
-      <c r="H50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I50" s="4" t="n"/>
+      <c r="H50" s="4" t="n"/>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J50" s="4" t="n"/>
       <c r="K50" s="4" t="inlineStr">
         <is>
@@ -58045,12 +58321,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H51" s="4" t="n"/>
-      <c r="I51" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I51" s="4" t="n"/>
       <c r="J51" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -58165,12 +58441,12 @@
       <c r="E55" s="4" t="n"/>
       <c r="F55" s="4" t="n"/>
       <c r="G55" s="4" t="n"/>
-      <c r="H55" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I55" s="4" t="n"/>
+      <c r="H55" s="4" t="n"/>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J55" s="4" t="n"/>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -58285,12 +58561,12 @@
       <c r="E59" s="4" t="n"/>
       <c r="F59" s="4" t="n"/>
       <c r="G59" s="4" t="n"/>
-      <c r="H59" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I59" s="4" t="n"/>
+      <c r="H59" s="4" t="n"/>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -58411,12 +58687,12 @@
       </c>
       <c r="F62" s="4" t="n"/>
       <c r="G62" s="4" t="n"/>
-      <c r="H62" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I62" s="4" t="n"/>
+      <c r="H62" s="4" t="n"/>
+      <c r="I62" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J62" s="4" t="n"/>
       <c r="K62" s="4" t="inlineStr">
         <is>
@@ -58453,12 +58729,12 @@
         </is>
       </c>
       <c r="G63" s="4" t="n"/>
-      <c r="H63" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I63" s="4" t="n"/>
+      <c r="H63" s="4" t="n"/>
+      <c r="I63" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J63" s="4" t="n"/>
       <c r="K63" s="4" t="inlineStr">
         <is>
@@ -58573,12 +58849,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H67" s="4" t="n"/>
-      <c r="I67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I67" s="4" t="n"/>
       <c r="J67" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -58687,12 +58963,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H70" s="4" t="n"/>
-      <c r="I70" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I70" s="4" t="n"/>
       <c r="J70" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -58755,12 +59031,12 @@
       </c>
       <c r="F72" s="4" t="n"/>
       <c r="G72" s="4" t="n"/>
-      <c r="H72" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I72" s="4" t="n"/>
+      <c r="H72" s="4" t="n"/>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -58843,12 +59119,12 @@
       </c>
       <c r="F74" s="4" t="n"/>
       <c r="G74" s="4" t="n"/>
-      <c r="H74" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I74" s="4" t="n"/>
+      <c r="H74" s="4" t="n"/>
+      <c r="I74" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J74" s="4" t="n"/>
       <c r="K74" s="4" t="n"/>
       <c r="L74" s="4" t="n"/>
@@ -58877,12 +59153,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H75" s="4" t="n"/>
-      <c r="I75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I75" s="4" t="n"/>
       <c r="J75" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -58915,12 +59191,12 @@
       <c r="E76" s="4" t="n"/>
       <c r="F76" s="4" t="n"/>
       <c r="G76" s="4" t="n"/>
-      <c r="H76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I76" s="4" t="n"/>
+      <c r="H76" s="4" t="n"/>
+      <c r="I76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J76" s="4" t="n"/>
       <c r="K76" s="4" t="n"/>
       <c r="L76" s="4" t="inlineStr">
